--- a/docs/BIE_ERP_Documentation.xlsx
+++ b/docs/BIE_ERP_Documentation.xlsx
@@ -12,8 +12,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Settings" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Masters" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. HR Management" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables Reference" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Item Masters" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Attendance+Salary" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. Sales" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. Purchase" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. Stores" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables Reference" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Menu Index'!$A$5:$F$79</definedName>
@@ -24,9 +29,19 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'2. Masters'!$5:$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'3. HR Management'!$A$5:$J$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'3. HR Management'!$5:$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Tables Reference'!$A$5:$E$34</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Tables Reference'!$5:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Coverage'!$5:$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'4. Item Masters'!$A$5:$J$15</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'4. Item Masters'!$5:$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'5. Attendance+Salary'!$A$5:$J$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'5. Attendance+Salary'!$5:$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'6. Sales'!$A$5:$J$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'6. Sales'!$5:$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'7. Purchase'!$A$5:$J$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'7. Purchase'!$5:$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'8. Stores'!$A$5:$J$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'8. Stores'!$5:$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Tables Reference'!$A$5:$E$79</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Tables Reference'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'Coverage'!$5:$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -199,10 +214,10 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -577,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -686,72 +701,84 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Tables Reference</t>
+          <t>4. Item Masters</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Every table touched in this phase, what it holds, and which screens use it.</t>
+          <t>10 screens - the classification lists, the item record, kits, and the only screen that can change a price.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
+          <t>5. Attendance+Salary</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>5 screens - the biometric import, the payroll run, overtime and the PF return.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>6. Sales</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>2 screens - the versioned quotation and the sales order generated from it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>7. Purchase</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>2 screens - the direct purchase order, and the pricing step between an indent and an order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>8. Stores</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>4 screens - the indent, the GRN (the only screen that increases stock), the return and the challan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Tables Reference</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Every table touched in this phase, what it holds, and which screens use it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>Coverage</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Phase plan and progress, with live formulas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="12" customHeight="1">
-      <c r="A15" s="3" t="inlineStr"/>
-      <c r="B15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16" ht="12" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>THE ONE THING TO UNDERSTAND FIRST</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr"/>
-    </row>
-    <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>BIE is multi-BRANCH by COLUMN</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Most systems add a branch_id column and store one row per branch. BIE does not. It stores ONE ROW PER ITEM and gives each branch its own SET OF COLUMNS - ho_stock, kl_stock, rjpm_stock, and the same again for every price, discount, margin and bin location.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>mst_branch stores the names</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>The branch row does not hold the stock; it holds the NAME OF THE COLUMN that holds the stock. A screen reads branch_stock_field from mst_branch, gets back the text 'ho_stock', and builds its SQL around it. That substitution is every branch-aware query in BIE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Why it matters</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>When a figure looks right for one branch and wrong for another, this is why - the two branches are literally different columns, and a screen that hardcodes ho_stock is right at Head Office and wrong everywhere else.</t>
         </is>
       </c>
     </row>
@@ -762,216 +789,3299 @@
     <row r="21" ht="12" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>LEGEND</t>
+          <t>THE ONE THING TO UNDERSTAND FIRST</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr"/>
     </row>
-    <row r="22" ht="18" customHeight="1">
+    <row r="22" ht="42" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>R / W / RW</t>
+          <t>BIE is multi-BRANCH by COLUMN</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Table is Read / Written / both by that screen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
+          <t>Most systems add a branch_id column and store one row per branch. BIE does not. It stores ONE ROW PER ITEM and gives each branch its own SET OF COLUMNS - ho_stock, kl_stock, rjpm_stock, and the same again for every price, discount, margin and bin location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Soft delete</t>
+          <t>mst_branch stores the names</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>The dustbin icon sets a status column to 0 via inc/cis_ajax/jquery_delete_records.php (or jquery_delete_records_hr.php for HR). Nothing is physically removed, and lists filter on status = 1.</t>
+          <t>The branch row does not hold the stock; it holds the NAME OF THE COLUMN that holds the stock. A screen reads branch_stock_field from mst_branch, gets back the text 'ho_stock', and builds its SQL around it. That substitution is every branch-aware query in BIE.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>(W) on mst_ledger</t>
+          <t>Why it matters</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>The screen auto-creates an accounts ledger BEFORE writing the master row, and stores its ledger_id on the master.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>tbl_accounts</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>The single central double-entry journal. Every money movement in the system posts here; Day Book, Ledger Book and Trial Balance are three readings of it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>_temp tables</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Session-tagged staging for document lines while a form is open. Copied to the real table on save, then cleared.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="12" customHeight="1">
-      <c r="A27" s="3" t="inlineStr"/>
-      <c r="B27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28" ht="12" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>FIVE RULES THAT HOLD NEARLY EVERYWHERE</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr"/>
+          <t>When a figure looks right for one branch and wrong for another, this is why - the two branches are literally different columns, and a screen that hardcodes ho_stock is right at Head Office and wrong everywhere else.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="12" customHeight="1">
+      <c r="A25" s="3" t="inlineStr"/>
+      <c r="B25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26" ht="12" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>LEGEND</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>R / W / RW</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Table is Read / Written / both by that screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Soft delete</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>The dustbin icon sets a status column to 0 via inc/cis_ajax/jquery_delete_records.php (or jquery_delete_records_hr.php for HR). Nothing is physically removed, and lists filter on status = 1.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>1. Nothing is really deleted</t>
+          <t>(W) on mst_ledger</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Every master carries a status column; deleting sets it to 0. The one exception is tbl_user_rights, which is hard-deleted and rebuilt.</t>
+          <t>The screen auto-creates an accounts ledger BEFORE writing the master row, and stores its ledger_id on the master.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2. Customers and suppliers share a table</t>
+          <t>tbl_accounts</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Both are rows in mst_supplier_new - note the _new. supp_type: C = customer, S = supplier. There is no customer table.</t>
+          <t>The single central double-entry journal. Every money movement in the system posts here; Day Book, Ledger Book and Trial Balance are three readings of it.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
+          <t>_temp tables</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Session-tagged staging for document lines while a form is open. Copied to the real table on save, then cleared.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="12" customHeight="1">
+      <c r="A32" s="3" t="inlineStr"/>
+      <c r="B32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33" ht="12" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>FIVE RULES THAT HOLD NEARLY EVERYWHERE</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr"/>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>1. Nothing is really deleted</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Every master carries a status column; deleting sets it to 0. The one exception is tbl_user_rights, which is hard-deleted and rebuilt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>2. Customers and suppliers share a table</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Both are rows in mst_supplier_new - note the _new. supp_type: C = customer, S = supplier. There is no customer table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
           <t>3. A party or an employee is also a ledger</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Customer, supplier and employee masters INSERT their mst_ledger row FIRST, then store the new ledger_id on the master row.</t>
         </is>
       </c>
     </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>4. Documents with lines use a _temp staging table</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Lines are staged against your session id while you type, copied under the new header id on save, then cleared. Abandoned documents leave harmless orphan rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="42" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>5. Most forms write themselves</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Few screens contain a hand-written INSERT. CIS_InsertRecord and CIS_UpdateRecord DESCRIBE the table and keep only posted values whose NAME MATCHES A REAL COLUMN. So the name of the input box IS the name of the column - and a typo is silently dropped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="12" customHeight="1">
+      <c r="A39" s="3" t="inlineStr"/>
+      <c r="B39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40" ht="12" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>SCOPE</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Schema source</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>db/bie.sql - the current dump in the repository. 105 tables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Included</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Only files the live menu actually opens - 63 screens across 11 menus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Eight mst_sub_menu rows with no URL. Seven are hidden; one, Bank Account Details under Settings, is set to show but goes nowhere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Field detail</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>The fields that DRIVE behaviour, plus every table write in full. Not an exhaustive inventory of every input on every form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="12" customHeight="1">
+      <c r="A45" s="3" t="inlineStr"/>
+      <c r="B45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46" ht="12" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>WHAT ACTUALLY MOVES STOCK</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47" ht="42" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Only four screens change it</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>GRN (grn_add.php) puts stock UP. The three invoice screens - quo_invoice.php, dc_invoice.php, mng_invoice.php - put it DOWN. Nothing else in BIE touches tbl_item_stock's quantity columns, with one exception: Item Price Update writes the stock column too (see 4.10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="42" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Two gaps, not design</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>A DELIVERY CHALLAN takes goods out of the building and only the later invoice reduces stock, so anything despatched but not invoiced is counted twice. A PURCHASE RETURN sends goods back and NOTHING reduces stock at all, so the quantity stays up permanently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="42" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>When a figure is wrong</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Check in this order: (1) challans raised but not invoiced, (2) purchase returns, (3) a price change made through Item Price Update, (4) whether you are reading tbl_item_details.item_curr_stock (stale) instead of the branch column on tbl_item_stock (live).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="12" customHeight="1">
+      <c r="A50" s="3" t="inlineStr"/>
+      <c r="B50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Related system</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Benzear is the sister codebase this one was forked from. Benzear is multi-COMPANY and keys on company_id; BIE is multi-BRANCH and keys on branch_id. A few unused company_id columns survive in BIE from that fork.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menu 8  ·  Stores  (mm_id = 20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>4 screens, and the only place in BIE where stock goes UP. The GRN increases it; the store indent, the purchase return and the delivery challan all move nothing - and for the last two, that is a gap rather than a design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Sub-menu (form)</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>PHP file(s)</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>What it does (short)</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Tables used</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>What changes in the tables</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Full flow</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Where it reflects</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Key notes / traps</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="103.4615384615385" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Store Indent List</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>store_indent_list.php (list) &gt; store_indent_add.php (raise/edit, 712 lines) &gt; inc/datatable/ajax_SiList.php &gt; store_indent_print.php</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Request - NO PRICES, NO STOCK MOVEMENT</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>The store asking for something: items, quantities, a suggested supplier and a remark. No rates - that is what PO Prepare is for. Each line shows the CURRENT STOCK and the item's MOQ beside the quantity asked for.</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>tbl_store_indent (RW)
+tbl_store_indent_details (RW)
+tbl_item_details + tbl_item_stock (R)
+mst_supplier_new (R)
+mst_finyear + mst_branch (R)
+tbl_task_user (R)</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>INSERT tbl_store_indent (si_finyr, si_slno, si_refno, si_date, supp_id, si_remarks, branch_id, si_approve_id, si_status).
+DELETE + INSERT tbl_store_indent_details (si_id, item_id, si_qty, item_moq, item_uom, si_unit, curr_stock).
+UPDATE tbl_store_indent on edit.
+DELETE: status to 0.</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>1. Stores &gt; Store Indent List - indents for your branch.
+2. Add New; the reference is SI/0042/BIE/&lt;branch&gt;/&lt;finyear&gt;.
+3. Choose a suggested supplier if you have one in mind, set the date and a remark.
+4. Add lines: pick the item, enter the QUANTITY NEEDED. The screen shows the MOQ and the CURRENT STOCK at this branch, and stores the stock figure on the line.
+5. Save - header, then lines. The approver is looked up from tbl_task_user.
+6. Print with store_indent_print.php.
+7. The indent then appears on the PO Prepare List to be priced.</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>PO Prepare List; Purchase Order eventually, through the prepare sheet; store_indent_print.php; Store Stock reports as a pending requirement.</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>curr_stock ON THE LINE IS A SNAPSHOT, NOT A LINK - it records what the stock was the day the indent was written and is never updated. The live figure is always tbl_item_stock.&lt;branch&gt;_stock.
+The block that would have written purchase-order lines directly from the indent is still in store_indent_add.php, COMMENTED OUT. Indents reach an order only through PO Prepare.
+STOCK DOES NOT MOVE HERE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="172.3076923076923" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>GRN List</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>grn_list.php (list) &gt; grn_add.php (receive, 1,161 lines) &gt; inc/datatable/ajaxGrnList.php &gt; grn_view.php &gt; grn_print.php &gt; inc/cis_ajax/jquery_modal_grn_cancel_reason.php &gt; purchase_return_add.php</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>STOCK MOVEMENT - IN. The only screen that increases stock</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Goods have arrived against a purchase order. Per line you record RECEIVED, ACCEPTED, REJECTED and PENDING. The accepted quantity is added to YOUR BRANCH's stock column - the screen reads the column name out of mst_branch and builds the SQL from it.</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>tbl_grn (RW)
+tbl_grn_details (RW)
+tbl_item_stock (W - &lt;branch&gt;_stock increased)
+tbl_stock_flow (W - one audit row per line)
+tbl_purchase_order (W - marked as received against)
+tbl_item_details (R - cost price; the stock update on this table is COMMENTED OUT)
+mst_branch (R - branch_stock_field)
+mst_supplier_new (R)
+mst_finyear (R)</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>INSERT tbl_grn (grn_slno, grn_finyr, grn_refno, grn_ref_code, grn_date, supp_id, branch_id, po_id).
+DELETE + INSERT tbl_grn_details - received, accepted, rejected, pending.
+PER LINE:
+  read branch_stock_field from mst_branch;
+  INSERT tbl_stock_flow (trans_type = 'GRN', trans_id, branch_id, item_id, item_price, before_qty, rcvd_qty, trans_qty, reje_qty, pend_qty, after_qty);
+  RE-READ the current stock from the database;
+  UPDATE tbl_item_stock SET &lt;branch_stock_field&gt; = current + accepted WHERE item_id = ...
+UPDATE tbl_purchase_order - received against.
+UPDATE tbl_grn SET rtn_submit_status = 1 when a purchase return is raised.</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>1. From the Direct PO List or the GRN List choose Add GRN against an APPROVED purchase order.
+2. The order's lines load with their ordered quantities. The reference is GRN/0042/BIE/&lt;branch&gt;/&lt;finyear&gt;; the serial is MAX + 1 within your branch AND financial year.
+3. For every line enter RECEIVED, ACCEPTED, REJECTED and PENDING. Accepted is what enters stock.
+4. Save - header, then lines, then the per-line stock block above.
+5. From the list: print, view, raise a purchase return, or cancel with a reason.</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>EVERY STOCK FIGURE IN THE SYSTEM - the item picker on quotations, orders and invoices; Store Stock List, Branch Wise Stock, Item Stock History; Purchase Return; GRN Payment Details; grn_print.php.</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>THE STOCK UPDATE ITSELF IS SOUND - the code RE-READS the current quantity from the database immediately before adding to it, rather than trusting the browser. Two GRNs saved at the same moment both land. Several other screens in BIE do not do this.
+THE AUDIT ROW CAN DISAGREE WITH THE STOCK: tbl_stock_flow.before_qty is taken from item_curr_stock AS THE BROWSER POSTED IT (read when the form was opened) and after_qty is that plus accepted. The real update re-reads. So the stock is right and the AUDIT TRAIL IS WRONG if anything moved meanwhile. Treat tbl_stock_flow as a record of what was received, not a running balance.
+THE VALUE ON THE AUDIT ROW USES A STALE PRICE - item_price comes from tbl_item_details.item_cost_price, written when the item was created and never updated.
+REJECTED AND PENDING QUANTITIES MOVE NOTHING AND ARE NOT CHASED - no screen lists outstanding pending quantities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="135.7692307692308" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Purchase Return List</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>purchase_return_list.php (list) &gt; purchase_return_add.php (raise, 717 lines) &gt; inc/datatable/ajaxPurchaseReturnList.php &gt; purchase_return_view.php &gt; inc/cis_ajax/jquery_modal_grn_cancel_reason.php</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Transaction - AND IT DOES NOT MOVE STOCK</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Goods received on a GRN are being sent back to the supplier. Raised AGAINST A GRN, so the lines and quantities are already known. The GRN is flagged as having a return against it.</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>tbl_purchase_return (RW)
+tbl_purchase_return_details (RW)
+tbl_grn (W - rtn_submit_status = 1)
+tbl_grn_details_temp (staging)
+tbl_item_details (R)
+mst_supplier_new (R)
+mst_finyear (R)</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>INSERT tbl_purchase_return - header: reference, date, grn_id, supp_id, remarks.
+DELETE + INSERT tbl_purchase_return_details - the returned lines.
+DELETE FROM tbl_grn_details_temp - the staging rows.
+UPDATE tbl_grn SET rtn_submit_status = 1.
+NO UPDATE TO tbl_item_stock. NO INSERT TO tbl_stock_flow. NO tbl_accounts ENTRY.</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>1. From the GRN List, open a GRN and choose Purchase Return.
+2. Tick the lines going back; enter the QUANTITY and the REASON for each. Lines are staged in tbl_grn_details_temp.
+3. Save - header and return lines written, staging cleared, GRN stamped rtn_submit_status = 1.
+4. View a saved return with purchase_return_view.php.</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>GRN List - the GRN now shows a return against it; Purchase Return List; purchase_return_view.php. NOT the stock reports. NOT Item Stock History. NOT the item picker.</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>PURCHASE RETURN NEVER REDUCES STOCK. purchase_return_add.php contains NO reference to tbl_item_stock, branch_stock_field, item_curr_stock or tbl_stock_flow - the whole stock block is absent. EVERY PURCHASE RETURN LEAVES THAT ITEM'S STOCK OVERSTATED BY THE RETURNED QUANTITY, PERMANENTLY. Until it is fixed, reconcile by hand. The pattern to copy is in grn_add.php: read branch_stock_field, re-read the current quantity, subtract, and write a tbl_stock_flow row with trans_type = 'PRTN'.
+NOTHING REVERSES THE MONEY EITHER - no tbl_accounts entry, so the supplier's ledger still shows the full GRN value owing. A credit note must be raised separately in Accounts.
+rtn_submit_status is a flag, not a quantity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="125.7692307692308" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>DC List</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>dc_list.php (list) &gt; dc_add.php (raise, 1,244 lines) &gt; inc/datatable/ajaxDclist.php &gt; dc_print.php &gt; package_list.php &gt; dc_invoice.php &gt; inc/cis_ajax/jquery_modal_sales_det.php</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Despatch document - NO STOCK MOVEMENT</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Goods going out to a customer against a sales order. Records what is being sent and, unusually, HOW IT IS PACKED - which items go in which box, and what kind of box each one is.</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>tbl_dc (RW)
+tbl_dc_details (RW)
+tbl_dc_details_temp (staging)
+tbl_package_box_details (RW)
+tbl_package_box_details_temp (staging)
+tbl_sales_order (R for lines; W - dc_status = 1)
+tbl_dc_package_box (R - the box types)
+mst_customer_branch (R - the delivery address)
+tbl_item_details + tbl_item_stock (R - shown, not changed)</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>INSERT tbl_dc_details_temp and tbl_package_box_details_temp - lines and boxes as you add them, tagged with your session.
+INSERT tbl_dc - header: reference, date, so_id, supp_id, delivery branch, transport.
+DELETE + INSERT tbl_dc_details and tbl_package_box_details - the staged rows under the real dc_id.
+DELETE the two _temp tables for your session.
+UPDATE tbl_sales_order SET dc_status = 1.
+NO UPDATE TO tbl_item_stock - dc_invoice.php does that.</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>1. From the Sales Order List choose DC against an order.
+2. Set the challan date, the customer's DELIVERY BRANCH, and the transport details.
+3. Confirm the item lines and quantities being despatched - staged against your session.
+4. PACK IT: add boxes, choose each box's TYPE (from Box Type, 2.3), assign items to boxes - also staged.
+5. Save - header written, staged lines and boxes copied across under the new dc_id, staging cleared, sales order stamped dc_status = 1.
+6. Print the challan (dc_print.php) and the packing list (package_list.php).
+7. INVOICE IT - dc_invoice.php turns the challan into an invoice, AND THAT IS THE STEP THAT REDUCES STOCK.</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Invoice - dc_invoice.php, which reduces stock and posts to accounts; Sales Order List - dc_status = 1; dc_print.php; package_list.php; sales reports.</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>BETWEEN THE CHALLAN AND THE INVOICE, STOCK IS COUNTED TWICE - the goods are on the van and the system still has them on the shelf. On a branch that despatches daily and invoices weekly, the overstatement is a week's despatches. When a stock count does not match, list the challans with no invoice first.
+THE PACKING LAYER IS OPTIONAL AND NOTHING CHECKS IT - a challan can be saved with lines and no boxes, or boxes that do not account for every line.
+Abandoning a half-built challan leaves rows in both _temp tables.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:J9"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E79"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tables Reference - Phases 1 and 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Every table touched so far. The system has 105 tables in total; the rest arrive with Accounts, Report and Service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Cols</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>What it holds</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Used by</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>tbl_user</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Logins. usr_type 'A' = administrator (bypasses rights). branch_id fixes the branch. pw_hint holds the password IN CLEAR.</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>1.1, 3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>tbl_user_rights</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>permissions</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>One row per permitted (user, menu, sub-menu). DRAWS THE SIDEBAR. The only HARD-deleted table in BIE.</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>1.1, sidebar.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>mst_main_menu</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>menu</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Top-level menus. mm_show = 1 to appear, mm_index orders them.</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>1.1, sidebar.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>mst_sub_menu</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>menu</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Sub-menu entries and the file each opens. sm_show = 1 required, or the item is hidden.</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>1.1, sidebar.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>mst_branch</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>THE KEY TABLE. Three branches, their letterhead, and FIFTY COLUMN NAMES pointing into tbl_item_stock.</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>1.2, and indirectly every stock and pricing screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>mst_supplier_new</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>CUSTOMERS AND SUPPLIERS TOGETHER. supp_type 'C' / 'S'. supp_approve_status gates purchase. discount_apply set from Common Settings.</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>1.3, 2.1, 2.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>mst_customer_branch</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Delivery branches of a customer.</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>mst_customer_branch_temp</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>staging</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Session-tagged branch rows while the customer form is open.</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>mst_ledger</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Accounts ledgers. Auto-created for every customer, supplier and employee BEFORE the master row.</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>2.1, 2.2, 3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>mst_accounts_group</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Ledger groups; supplies ledger_type. Maintained in Accounts.</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>2.1, 2.2, 3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>tbl_dc_package_box</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>lookup</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Packing box types for delivery challans.</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>mst_state</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>lookup</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>States and GST state codes - drives CGST/SGST vs IGST.</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>mst_district</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>lookup</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Districts within a state.</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>mst_city</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>lookup</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Cities within a district.</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>mst_department</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>lookup</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Departments. Status column is rec_del_status.</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>2.7, 3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>mst_designation</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>lookup</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Job titles within a department.</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>2.8, 3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>tbl_month_master</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Per month: total days, WORKING DAYS, holidays, function holidays. The payroll divisor.</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>2.9, and all four attendance reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>mst_finyear</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Financial years. Serials restart within each; the active year goes into supplier and advance codes.</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>2.2, 3.7, 3.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>mst_employee</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>~65</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>The employee record. bio_id is the link to imported attendance; emp_type 1 Staff / 2 Labour / 3 Others.</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>3.1, 3.2, 3.4-3.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>mst_employee_certificate</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Uploaded certificates per employee. STAFF ONLY - the insert is guarded by emp_type == 1.</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>tbl_asset_details</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Company assets issued to an employee. Rebuilt on every edit.</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>mst_labour</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>lookup</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Labour groups or contractors. Still carries an unused company_id from the Benzear fork.</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>3.2.1, 3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>mst_salary_setting</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Salary packages - the PERCENTAGES that split earned pay, not amounts. sal_period 2 = the CTC is monthly.</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>tbl_emp_advance</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>transaction</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>Advances paid to employees, with running balance. advance_status 3 = treated as settled.</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>tbl_emp_advance_return_payment</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>transaction</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Recoveries against an advance, tagged with the attendance month and year.</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>3.5, attendance reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>tbl_emp_debit_note</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>transaction</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Charges raised against employees.</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+    </row>
     <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>4. Documents with lines use a _temp staging table</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Lines are staged against your session id while you type, copied under the new header id on save, then cleared. Abandoned documents leave harmless orphan rows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="42" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>5. Most forms write themselves</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Few screens contain a hand-written INSERT. CIS_InsertRecord and CIS_UpdateRecord DESCRIBE the table and keep only posted values whose NAME MATCHES A REAL COLUMN. So the name of the input box IS the name of the column - and a typo is silently dropped.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="12" customHeight="1">
-      <c r="A34" s="3" t="inlineStr"/>
-      <c r="B34" s="4" t="inlineStr"/>
-    </row>
-    <row r="35" ht="12" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>SCOPE</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr"/>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Schema source</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>db/bie.sql - the current dump in the repository. 105 tables.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Included</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Only files the live menu actually opens - 63 screens across 11 menus.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>Eight mst_sub_menu rows with no URL. Seven are hidden; one, Bank Account Details under Settings, is set to show but goes nowhere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Field detail</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>The fields that DRIVE behaviour, plus every table write in full. Not an exhaustive inventory of every input on every form.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Related system</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>Benzear is the sister codebase this one was forked from. Benzear is multi-COMPANY and keys on company_id; BIE is multi-BRANCH and keys on branch_id. A few unused company_id columns survive in BIE from that fork.</t>
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>tbl_accounts</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>THE CENTRAL DOUBLE-ENTRY JOURNAL. Every money movement posts here; Day Book, Ledger Book and Trial Balance are three readings of it.</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>3.5, 3.6 (and most of the system)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>mst_shifts</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>The two shifts and the six clock times that define each. Turns a punch into a present, a late or an overtime.</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>3.7, Import Attendance, all attendance reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>tbl_item_stock</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>many</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>One row per item, with a BLOCK OF COLUMNS PER BRANCH. Not written in Phase 1, but mst_branch is entirely about it.</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>(Phase 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>mst_principal</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>lookup</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>Manufacturers / brand owners.</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>mst_division</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>lookup</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Product divisions.</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>mst_category</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>lookup</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>Item categories, optionally tied to an item type.</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>mst_brand</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>lookup</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Brands and makes.</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>mst_uom</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>lookup</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Units of measure. uom_code is what prints.</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>mst_color</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>lookup</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Colours.</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>mst_hsn</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>lookup</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>HSN / SAC codes AND THE THREE GST RATES. Editing a rate changes old reprints.</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>tbl_item_details</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>WHAT THE ITEM IS. Its price and stock columns are STALE leftovers - see 4.1. branch_id is a CSV list of branches.</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>4.8, and read by every document screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>tbl_item_stock</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>many</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>WHAT IT COSTS AND HOW MANY THERE ARE, PER BRANCH. One row per item, a block of columns per branch. The live figures.</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>4.8, 4.10, 8.2, and every invoice</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>tbl_itemprice_history</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>versioned</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>many</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>One row per price change per branch, holding BOTH the new (&lt;branch&gt;_new_*) and old (&lt;branch&gt;_old_*) figures.</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>tbl_multiuom_itemprice_history</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>versioned</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>The same, for items priced in more than one unit.</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>tbl_item_group</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Kit headers.</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>tbl_item_group_details</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>One row per item in a kit, with its quantity.</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>tbl_item_group_details_temp</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>staging</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Session-tagged kit lines while the form is open.</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>tbl_stock_flow</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>One row per stock movement. before_qty / after_qty come from the BROWSER and can disagree with the real stock - see 8.2.</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>8.2, and the invoice screens</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>tbl_attendance_import_new</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>import</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Raw biometric punches, one row per punch. sync_status marks a punch as processed.</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>tbl_attendance</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>transaction</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>One row per employee per work date: check in / out, work_time, late_in, early_out - all in MINUTES.</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>5.1, 5.2, 5.3, 5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>tbl_emp_salary</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>versioned</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>ONE ROW PER SALARY REVISION; current flagged em_current = 1. Holds emp_ctc and the package.</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>3.4, 5.2, 5.3, 5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>tbl_emp_monthly_salary</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>transaction</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>many</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>THE FROZEN PAYSLIP. salary_type WPF / WOPF / OT. Written only by issue_salary.php.</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>5.2, 5.3, 5.4, 5.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>tbl_emp_debit_note_return_payment</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>transaction</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>Recoveries against a debit note, tagged with the attendance month.</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>5.2, 5.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>tbl_quotation</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>transaction</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>VERSIONED. quo_slno + quo_version identify a quotation; prev_quo_id chains the versions. branch_id = customer's branch, bie_branch_id = BIE's.</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>tbl_quotation_details</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>Quotation lines. Rebuilt on every save.</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>tbl_quo_pack_details</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>Quotation packing details.</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>tbl_sales_order</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>transaction</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>Always carries quo_id - there is no standalone sales order. dc_status is a flag, not a count.</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>tbl_sales_order_details</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>Sales order lines.</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>tbl_sales_order_pack_dts</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>Sales order packing details.</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>tbl_purchase_order</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>transaction</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>po_slno is MAX + 1 PER BRANCH. po_approve_id is frozen at creation.</t>
+        </is>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>tbl_purchase_order_details</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>PO lines with rate, discount, tax and net.</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>tbl_po_print_details</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>Terms and text printed on the order.</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>tbl_po_prepare</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>transaction</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>One sheet per store indent being priced. Carries si_id.</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>tbl_po_prepare_dets</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>ONE SUPPLIER AND PRICE PER LINE - the point of the screen.</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>tbl_store_indent</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>transaction</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>The store's request. No prices.</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>tbl_store_indent_details</t>
+        </is>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>Lines with si_qty, item_moq and curr_stock (a SNAPSHOT, not live).</t>
+        </is>
+      </c>
+      <c r="E67" s="10" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>tbl_grn</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>transaction</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Goods receipt. grn_slno is MAX + 1 per branch AND financial year. rtn_submit_status flags a return.</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>tbl_grn_details</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>Received / accepted / rejected / pending per line. ONLY ACCEPTED MOVES STOCK.</t>
+        </is>
+      </c>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>tbl_grn_details_temp</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>staging</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>Staging while a purchase return is built.</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t>tbl_purchase_return</t>
+        </is>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>transaction</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>Always carries grn_id. WRITES NO STOCK AND NO ACCOUNTS ENTRY - see 8.3.</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>tbl_purchase_return_details</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>Returned lines with quantity and reason.</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>tbl_dc</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>transaction</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>Delivery challan. Always carries so_id. MOVES NO STOCK.</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>tbl_dc_details</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>Challan lines.</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t>tbl_dc_details_temp</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>staging</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>Session-tagged challan lines.</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t>tbl_package_box_details</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>One row per box on a challan - its type and contents.</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>tbl_package_box_details_temp</t>
+        </is>
+      </c>
+      <c r="B77" s="10" t="inlineStr">
+        <is>
+          <t>staging</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>Session-tagged boxes.</t>
+        </is>
+      </c>
+      <c r="E77" s="10" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t>tbl_task_user</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>routing</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>Who approves what. 1 PO Approval, 2 Supplier Approval, 3 Quotation Approval - BUT ROW 3 IS NEVER READ (see 6.1).</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>6.1, 7.1, 7.2, 8.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>tbl_invoice</t>
+        </is>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>transaction</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>The invoice. THE STEP THAT REDUCES STOCK. Covered in Part 9.</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>(Phase 3)</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A5:E79"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Coverage tracker</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Menu order follows the sidebar. Update the Status column as each phase lands - the totals below recalculate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Main menu</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>mm_id</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Screens</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Word part</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Part 1</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Administrators only. One menu item has no file behind it</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Masters</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Part 2</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>Month Master is the payroll calendar, not a lookup</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>HR Management</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Part 3</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Item Masters</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Part 4</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>The item record creates the branch stock row</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Attendance and Salary</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Part 5</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Nothing is frozen until Issue Salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Part 6</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>Stock does not move until the invoice</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Purchase</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Part 7</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Stores</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Part 8</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>Where stock actually moves</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Accounts</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Part 9</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>Part 10</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="G15" s="16" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>Largest menu - 14 reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Part 11</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Menus in the system</t>
+        </is>
+      </c>
+      <c r="C18" s="18">
+        <f>COUNTA(B6:B16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Menus documented</t>
+        </is>
+      </c>
+      <c r="C19" s="18">
+        <f>COUNTIF(G6:G16,"Done")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>Screens in the system</t>
+        </is>
+      </c>
+      <c r="C20" s="18">
+        <f>SUM(D6:D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>Screens documented</t>
+        </is>
+      </c>
+      <c r="C21" s="18">
+        <f>SUMIF(G6:G16,"Done",D6:D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>Screens remaining</t>
+        </is>
+      </c>
+      <c r="C22" s="18">
+        <f>SUMIF(G6:G16,"Pending",D6:D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>Percent complete</t>
+        </is>
+      </c>
+      <c r="C23" s="19">
+        <f>IFERROR(SUMIF(G6:G16,"Done",D6:D16)/SUM(D6:D16),0)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="A22:B22"/>
+  </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -3448,7 +6558,7 @@
     <row r="8" ht="64" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
@@ -3503,7 +6613,7 @@
     <row r="9" ht="64" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.2.1</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
@@ -3556,10 +6666,10 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="83.26923076923076" customHeight="1">
+    <row r="10" ht="142.8846153846154" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
@@ -3579,7 +6689,7 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>A named breakdown of pay: basic, DA, HRA, conveyance, PF and CCA. Define it once, attach people to it. Either MONTHLY or DAILY, which changes what the figures mean.</t>
+          <t>How a salary is SPLIT UP - what share is basic, DA, HRA, conveyance and CCA, and what rate of PF applies. The six figures are PERCENTAGES, NOT AMOUNTS: the shipped packages all read 40, 25, 25, 10, 12. The amount itself lives on the employee (3.4). By convention packages are NAMED after the CTC they go with - 18000, 20000 - but that is a habit, not something the code reads.</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -3596,10 +6706,11 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>1. HR Management &gt; Salary Package - name, type and components.
+          <t>1. HR Management &gt; Salary Package - name, type and the percentages.
 2. Add New opens mst_salary_package_add.php.
-3. Name it, choose Monthly (M) or Daily (D), set the period, enter the six amounts.
-4. Save - one row, straight in.</t>
+3. Name it, choose Monthly (M) or Daily (D), set the period, enter the six PERCENTAGES.
+4. Save - one row, straight in.
+HOW THEY ARE USED: basic = earned x sal_basic%, and the same for DA, HRA and conveyance; then EPF = (basic + DA) x sal_pf%. The percentages decide the SPLIT and the PF DEDUCTION, never the total.</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
@@ -3609,73 +6720,79 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>EVERY COMPONENT IS decimal(6,2) - the largest value that fits is 9999.99. A basic above ten thousand cannot be stored; MySQL refuses or silently clamps depending on strict mode, and nothing on the screen warns you.
-EDITING A PACKAGE CHANGES PAY FOR EVERYBODY ON IT, INCLUDING PAST MONTHS - the reports read the current row each time they open; nothing is frozen at month end. To change one person's pay, move them to another package.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="86.34615384615384" customHeight="1">
+          <t>sal_period IS THE FIELD THAT MATTERS: 2 means the CTC is a MONTHLY figure, so earned pay is CTC / working days x days paid; anything else means the CTC is a DAILY RATE, so earned pay is CTC x days paid. sal_type (M/D) is only a label - the calculation does not read it.
+NOTHING CHECKS THAT THE PERCENTAGES ADD UP TO 100. Enter figures summing to 90 and the payslip shows components that do not add up to the net - no warning, no error.
+EDITING A PACKAGE CHANGES PAY FOR EVERYBODY ON IT, INCLUDING PAST MONTHS - the reports read the current row each time they open; nothing is frozen at month end. To change one person's pay, change their CTC in Employee Salary Setting, which IS versioned; only change a package when the SPLIT itself is wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="139.0384615384615" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Employee Salary</t>
+          <t>Employee Salary Setting</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>employee_salary.php + inc/datatable/ajaxEmployeeSalarySet.php + modal_employee_det.php</t>
+          <t>employee_salary.php (list) &gt; emp_setsalary.php (THE ACTUAL SETTING SCREEN) &gt; inc/datatable/ajaxEmployeeSalarySet.php &gt; modal_employee_det.php</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>READ ONLY</t>
+          <t>Versioned transaction - WITHOUT A ROW HERE, AN EMPLOYEE HAS NO PAY</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>Every employee with their CTC, searchable and filterable by branch and employee type. Despite the name this is NOT where salary is set or run.</t>
+          <t>The list answers 'what is everyone on?' - code, name, department, designation, CTC. Click through and you set the employee's CTC, the salary package that says how it splits, their OT rate, their casual leave, and the date it takes effect. Saving does NOT overwrite - it retires the old row and writes a new one.</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>mst_employee (R - emp_ctc)
-mst_department (R)
-mst_designation (R)</t>
+          <t>tbl_emp_salary (RW - one row per revision, live one flagged em_current = 1)
+mst_employee (W - emp_ctc and em_id cached onto the employee row)
+mst_salary_setting (R - the package dropdown)
+mst_department / mst_designation (R)</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>NOTHING. This screen writes nothing at all.</t>
+          <t>UPDATE tbl_emp_salary SET em_current = 0 WHERE emp_id = &lt;this employee&gt; - RETIRES the old revision, does not delete it.
+INSERT tbl_emp_salary (emp_id, sal_id, emp_ctc, emp_ot_sal, emp_cl, is_allow_fh, em_from, em_current = 1, em_remarks, em_update_by, em_date_time).
+UPDATE mst_employee SET emp_ctc = :emp_ctc, em_id = :em_id - a cached copy pointing at the new current revision.</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>1. HR Management &gt; Employee Salary.
-2. Search by employee name, code, mobile, department or designation; filter by branch and employee type.
-3. One line per employee: code, name, department, designation, CTC.
-4. The eye icon opens the full employee record in a modal.</t>
+          <t>1. HR Management &gt; Employee Salary Setting. Search by name, code, mobile, department or designation; filter by branch and employee type.
+2. Click through to emp_setsalary.php for one employee - current figures plus the full history of past revisions.
+3. Enter the new CTC, choose the SALARY PACKAGE, set the OT rate, the casual leave figure and whether function holidays are allowed; give the effective-from date and a remark.
+4. Save - old rows retired, new row inserted, mst_employee pointed at it.
+5. The new CTC is used by the next attendance report you run.</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>Nothing - it is a view.</t>
+          <t>Attendance Report (PF) and (Without PF) - earned pay is CTC / working days x days paid, then split by the package percentages; OT Report via emp_ot_sal; EPF Report - PF is a percentage of basic + DA, both derived from this CTC; this list; the employee's own record.</t>
         </is>
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
-          <t>WHERE SALARY ACTUALLY HAPPENS: the figures come from the Salary Package attached to the employee, apportioned by the days in Month Master and the punches from Import Attendance; the four Attendance and Salary reports do the calculation.
-emp_ctc is a column on mst_employee, but the Employee form does not offer it and this screen does not edit it - in the shipped code it is set directly in the database. If CTC shows zero for everyone, that is why.</t>
+          <t>AN EMPLOYEE WITH NO ROW HERE IS PAID NOTHING. The Employee form does not ask for CTC, so a new employee has none until someone comes to this screen. The attendance reports list them with zeros rather than warn you.
+TWO COPIES OF THE CTC EXIST and are written together: the real one on the current tbl_emp_salary row, and a cached copy on mst_employee.emp_ctc. The list shows the cached copy; the payroll reports read the real one. A direct database edit to mst_employee.emp_ctc changes what you see and not what is paid.
+THIS IS THE em_current PATTERN - never overwrite, retire the old row and insert a new one, then cache the pointer on the parent. tbl_emp_advance and tbl_emp_debit_note use the same idea with is_current.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="132.6923076923077" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
@@ -3740,7 +6857,7 @@
     <row r="13" ht="68.46153846153845" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
@@ -3794,15 +6911,15 @@
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>THE SAME CAVEATS AS EMPLOYEE ADVANCE - the two screens share their code: a part-recovery can mark it settled (debit_status = 3), there is no cancel or correct, and the list and the entry screen can disagree.
+          <t>THE SAME CAVEATS AS EMPLOYEE ADVANCE (3.5) - the two screens share their code: a part-recovery can mark it settled (debit_status = 3), there is no cancel or correct, and the list and the entry screen can disagree.
 A debit note is a real accounting charge, not a note to self - it hits the employee's ledger and the Trial Balance the moment you save.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="157.8846153846154" customHeight="1">
+    <row r="14" ht="180.3846153846154" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
@@ -3822,7 +6939,7 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Two shifts, DAY and NIGHT, and the exact clock times that define each. This is what turns a raw biometric punch into a present, a late or an overtime. Each shift carries SIX times: the official check-in and check-out plus a WINDOW around each - a punch outside the window is not counted as that shift at all.</t>
+          <t>Two shifts, DAY and NIGHT, and the clock times that define each. The official check_in and check_out are what the attendance import measures lateness against. Each row ALSO carries a window around each time, a duration, and a next-day flag - they are on the form and they save, but NOTHING READS THEM.</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -3846,15 +6963,15 @@
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Import Attendance - each punch is matched against these windows to decide which shift it belongs to and whether it counts; Attendance Report (PF) and (Without PF) - present, absent and half-day come out of this; OT Report - overtime is time worked beyond duration.</t>
+          <t>Import Attendance - after pairing punches into a check-in and a check-out it reads this row and works out late_in, late_out, early_in and early_out in MINUTES; Attendance Report (PF) and (Without PF) - those minutes feed present, absent and half-day; OT Report - overtime is derived from the recorded work time.</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>THE WINDOWS ARE NARROW AND A PUNCH OUTSIDE THEM IS THROWN AWAY. DAY's check-in window closes at 09:05, so someone punching at 09:15 has NO check-in that day and shows ABSENT, not late. If a whole group shows absent on a day they worked, widen check_in_end and import again.
-CHANGING THESE TIMES CHANGES ATTENDANCE ALREADY IMPORTED AND REPORTED - the reports re-derive everything from mst_shifts each run. Make changes at a month boundary and print anything you need first.
-is_nxtday_checkout = 1 IS WHAT MAKES THE NIGHT SHIFT WORK - a 19:00 check-in pairs with a 07:00 check-out the next morning. Without it, twelve hours look like absence.
-Shipped data: DAY 09:00-17:30, window 08:00-09:05 in and 17:30-23:00 out, duration 510. NIGHT 19:00-07:00, window 18:00-20:00 in and 06:00-08:00 out, duration 540, next-day flag 1.</t>
+          <t>SIX OF THE EIGHT FIELDS ON THIS FORM DO NOTHING. The import fetches the shift row and uses ONLY check_in and check_out, to work out how many minutes late or early someone was. The four window fields are fetched in the same query and never looked at; duration and work_day are read by nothing; and NO FILE IN BIE READS is_nxtday_checkout AT ALL. Changing them is harmless and pointless.
+THE NIGHT SHIFT IS NEVER ASSIGNED: import_attendance.php sets shift_id = 1 for every punch, so everyone is treated as DAY shift whatever time they worked. A night worker checking in at 19:00 is measured against DAY's 09:00 start and comes out enormously late. Until the import chooses a shift, editing the NIGHT row changes nothing.
+CHANGING check_in OR check_out CHANGES ATTENDANCE ALREADY IMPORTED - the late and early minutes are recalculated whenever a row is reprocessed.
+Shipped data: DAY 09:00-17:30 duration 510; NIGHT 19:00-07:00 duration 540.</t>
         </is>
       </c>
     </row>
@@ -3871,27 +6988,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="74" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tables Reference - Phase 1</t>
+          <t>Menu 4  ·  Item Masters  (mm_id = 3)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every table touched so far. The system has 105 tables in total; the rest arrive with the later menus.</t>
+          <t>10 screens. Six one-field lists, HSN (which sets the tax), the item record - which creates the branch stock row - kits, and the price-change screen. An item lives in TWO tables: tbl_item_details says what it is, tbl_item_stock says what it costs and how many there are, per branch. The price and stock columns on tbl_item_details are STALE.</t>
         </is>
       </c>
     </row>
@@ -3899,815 +7021,636 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>#</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Kind</t>
+          <t>Sub-menu (form)</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Cols</t>
+          <t>PHP file(s)</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>What it holds</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Used by</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>tbl_user</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>master</t>
+          <t>What it does (short)</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Tables used</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>What changes in the tables</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Full flow</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Where it reflects</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Key notes / traps</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="64" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Principal</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>mst_principal.php</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Logins. usr_type 'A' = administrator (bypasses rights). branch_id fixes the branch. pw_hint holds the password IN CLEAR.</t>
+          <t>Lookup</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>1.1, 3.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>tbl_user_rights</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>permissions</t>
+          <t>The manufacturer or brand owner whose products these are.</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>mst_principal (RW)</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>INSERT / UPDATE mst_principal (principal_name, principal_code).
+DELETE: UPDATE principal_status = 0.</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>1. Open - live principals listed.
+2. Type name and code, Save.
+3. The pencil loads the row back.</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Item Details - the Principal dropdown; a filter on the item list and on stock reports.</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>Name and code are both free text and neither is checked for uniqueness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="64" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Division</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>mst_division.php</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>One row per permitted (user, menu, sub-menu). DRAWS THE SIDEBAR. The only HARD-deleted table in BIE.</t>
+          <t>Lookup</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>1.1, sidebar.php</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>mst_main_menu</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>menu</t>
+          <t>The product division an item belongs to.</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>mst_division (RW)</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>INSERT / UPDATE mst_division (division_name, division_code, audit pair).
+DELETE: UPDATE division_status = 0.</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>1. Open - live divisions listed.
+2. Type name and code, Save.</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Item Details - the Division dropdown; grouping on sales and stock reports.</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr"/>
+    </row>
+    <row r="8" ht="64" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Category</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>mst_category.php</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Top-level menus. mm_show = 1 to appear, mm_index orders them.</t>
+          <t>Lookup</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>1.1, sidebar.php</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>mst_sub_menu</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>menu</t>
+          <t>The item category. Also carries an item_type_id, so a category can be tied to a kind of item.</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>mst_category (RW)</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>INSERT / UPDATE mst_category (item_type_id, category_name, category_code, audit pair).
+DELETE: UPDATE category_status = 0.</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>1. Open - live categories listed.
+2. Type name and code, Save.</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>Item Details - the Category dropdown; a filter on the item list, the stock reports and the cost worksheet.</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9" ht="64" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Brand / Make</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>mst_brand.php</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Sub-menu entries and the file each opens. sm_show = 1 required, or the item is hidden.</t>
+          <t>Lookup</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>1.1, sidebar.php</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>mst_branch</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>master</t>
+          <t>The brand or make.</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>mst_brand (RW)</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>INSERT / UPDATE mst_brand (brand_name, brand_code, audit pair).
+DELETE: UPDATE brand_status = 0.</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>1. Open - live brands listed.
+2. Type name and code, Save.</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Item Details - the Brand / Make dropdown; printed on quotations and invoices.</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10" ht="64" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Unit of Measurement (UOM)</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>mst_uom.php</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>THE KEY TABLE. Three branches, their letterhead, and FIFTY COLUMN NAMES pointing into tbl_item_stock.</t>
+          <t>Lookup</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>1.2, and indirectly every stock and pricing screen</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>mst_supplier_new</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>master</t>
+          <t>Nos, Kg, Metre, Litre and so on. uom_code is the short form that prints on documents.</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>mst_uom (RW)</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>INSERT / UPDATE mst_uom (uom_name, uom_code, audit pair).
+DELETE: UPDATE uom_status = 0.</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>1. Open - live units listed.
+2. Type the name and the 5-character code, Save.</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Item Details; Item Grouping; the UOM column on every quotation, sales order, PO, GRN, delivery challan and invoice line.</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>uom_code is only 5 characters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="64" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Colour</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>mst_color.php</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>CUSTOMERS AND SUPPLIERS TOGETHER. supp_type 'C' / 'S'. supp_approve_status gates purchase. discount_apply set from Common Settings.</t>
+          <t>Lookup</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>1.3, 2.1, 2.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>mst_customer_branch</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>child</t>
+          <t>The colour list.</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>mst_color (RW)</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>INSERT / UPDATE mst_color (color_name, color_code, audit pair).
+DELETE: UPDATE color_status = 0.</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>1. Open - live colours listed.
+2. Type name and code, Save.</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Item Details - the Colour dropdown.</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr"/>
+    </row>
+    <row r="12" ht="90.38461538461539" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>HSN</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>mst_hsn.php</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Delivery branches of a customer.</t>
+          <t>Lookup - BUT IT SETS THE TAX</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>2.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>mst_customer_branch_temp</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>staging</t>
+          <t>The HSN or SAC code, plus THE THREE GST RATES that go with it - CGST, SGST and IGST. The one screen in Item Masters with money riding on it.</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>mst_hsn (RW)</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>INSERT / UPDATE mst_hsn (hsn_type, hsn_code, hsn_description, cgst, sgst, igst).
+DELETE: UPDATE hsn_status = 0.</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>1. Open - live codes with their rates.
+2. Type the HSN code, a description, and the CGST, SGST and IGST percentages.
+3. Save. The pencil loads a row for correction.
+4. On the item form the HSN dropdown now offers it.</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>Item Details (tbl_item_details.item_hsn); the tax on every quotation, sales order and invoice line; the tax on purchase orders and GRNs; Item Price History records the HSN in force at the time.</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>CHANGING A RATE CHANGES IT EVERYWHERE, INCLUDING ON REPRINTS - documents store the HSN id and look the rates up at print time, so reprinting an old invoice after a rate change shows the NEW rate against the OLD total. Add a new HSN row instead of editing.
+Whether CGST+SGST or IGST applies is decided elsewhere, by comparing the customer's state_id with the branch's company_state_code. See the Rajapalayam warning in 1.2.
+Rates are decimal(6,2): enter 9 for 9 per cent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="185.1923076923077" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Item Details</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>lst_item_details.php (list) &gt; mst_item_details.php (add/edit, 1,023 lines) &gt; inc/datatable/ajaxItemDetailsList.php &gt; inc/cis_ajax/modal_items_dets.php (view) &gt; inc/cis_ajax/modal_update_items.php (price modal) &gt; inc/cis_ajax/jquery_modal_supp_map.php (supplier mapping) &gt; branch_wise_item_update.php (branch release)</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Session-tagged branch rows while the customer form is open.</t>
+          <t>Master - CREATES THE BRANCH STOCK ROW</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>2.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>mst_ledger</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>master</t>
+          <t>The item record: code, description, type, the six classifications, UOM, HSN, supplier, image, opening prices and quantities. Saving also creates the item's tbl_item_stock row and fills in the pricing columns FOR EVERY BRANCH AT ONCE.</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>tbl_item_details (RW)
+tbl_item_stock (W - created here)
+mst_branch (R - IN A LOOP, for the column names)
+mst_principal / mst_division / mst_category / mst_brand / mst_uom / mst_hsn / mst_color (R)
+mst_supplier_new (R)
+tbl_item_group (R)</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>INSERT tbl_item_details - the item. branch_id and branch_status are set FROM WHO YOU ARE (see traps).
+INSERT tbl_item_stock (item_id) - a bare row; ALL STOCK STARTS AT ZERO.
+Then, ONCE PER BRANCH, in a loop over mst_branch:
+  UPDATE tbl_item_stock SET &lt;branch_item_price&gt; = :price, &lt;branch_item_discount&gt; = :disc, &lt;branch_item_cost_price&gt; = :cost, &lt;branch_item_selling_price&gt; = :sell, &lt;branch_item_margin&gt; = :margin, &lt;branch_item_msq&gt; = :min, &lt;branch_item_maq&gt; = :max, &lt;branch_item_moq&gt; = :order WHERE stock_id = :stock_id
+  - the column NAMES come out of the branch row and are concatenated into the SQL.
+EDIT: UPDATE tbl_item_details ONLY - tbl_item_stock is NOT touched.
+BRANCH WISE ITEM UPDATE: UPDATE tbl_item_details SET branch_id = '&lt;csv list&gt;', branch_status = 1.
+DELETE: UPDATE item_status = 0 (the stock row stays).</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>1. Item Masters &gt; Item Details - active items, filterable by category, brand, principal and branch.
+2. Add New opens mst_item_details.php.
+3. Enter the ITEM CODE (you type it - it is not generated) and description.
+4. Choose the ITEM TYPE: 6 Consumable, 7 Group Products, 3 Raw Materials, 2 Trading, 8 Labour Charges.
+5. Pick principal, division, category, brand, colour, UOM and HSN; pick the supplier.
+6. Enter opening price, discount, cost price, selling price, margin, min / max / re-order quantities.
+7. Upload an image - renamed after the item code, stored under project_img/item_image/.
+8. Save - item row, then the bare stock row, then the branch loop.
+9. From the list, three action icons: view (modal), Item Price Update (mst_itemprice_history.php), Branch Wise Item Update (which branches may use this item).</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Quotation, Sales Order, Invoice - the item picker, which returns this branch's price and stock; Purchase Order, GRN, Store Indent - the same picker on the buying side; Item Grouping; Item Price History; all the stock reports.</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>EVERY BRANCH GETS THE SAME OPENING PRICE - the loop writes the one set of figures you typed into all three branches' columns. There is no per-branch price on the add form.
+AN ITEM CREATED ANYWHERE BUT HEAD OFFICE IS BORN INVISIBLE: the code sets branch_id = 1, branch_status = 1 if you are at HO, and branch_id = 0, branch_status = 0 otherwise. A Kerala user can create an item and not find it in any dropdown - including their own. Someone must open Branch Wise Item Update and tick the branches.
+EDITING AN ITEM NEVER TOUCHES tbl_item_stock - the branch loop is only in the SAVE path. Correcting a price by editing the item does NOTHING. Prices change only through Item Price Update.
+tbl_item_details.branch_id is a VARCHAR holding a COMMA-SEPARATED LIST of branch ids.
+The branch loop reads SELECT * FROM mst_branch with NO status filter, so a deleted branch still gets its columns written.
+item_code is typed, not generated, and is not checked for uniqueness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="90.96153846153845" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Item Grouping</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>lst_item_grouping.php (list) &gt; mst_item_grouping.php (add/edit, 620 lines) &gt; inc/datatable/ajaxItemGroupingList.php &gt; inc/cis_ajax/modal_item_group_det.php (view)</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Accounts ledgers. Auto-created for every customer, supplier and employee BEFORE the master row.</t>
+          <t>Master with child lines - a kit</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>2.1, 2.2, 3.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>mst_accounts_group</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>master</t>
+          <t>A named set of items with a quantity each. Sell or quote the group and all its parts come with it, in the right proportions.</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>tbl_item_group (RW)
+tbl_item_group_details (RW)
+tbl_item_group_details_temp (W - session staging)
+tbl_item_details (R)
+mst_uom (R)</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>INSERT tbl_item_group_details_temp - one row per line as you add it, tagged with your session.
+INSERT tbl_item_group - the header, item_group_slno = MAX + 1.
+DELETE FROM tbl_item_group_details WHERE item_group_id = &lt;this group&gt;.
+INSERT tbl_item_group_details - the staged lines under the real group id.
+DELETE FROM tbl_item_group_details_temp WHERE session_id = &lt;yours&gt;.
+UPDATE tbl_item_group on edit.</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>1. Item Masters &gt; Item Grouping - live groups with how many items each holds.
+2. Add New opens mst_item_grouping.php; the group serial is MAX(item_group_slno) + 1.
+3. Name the group, give it a code, pick its UOM, add remarks.
+4. Add items one at a time - item plus QUANTITY. Each goes into the _temp table against your session.
+5. Save - header written, staged lines copied across, staging cleared.
+6. On edit the existing detail rows are DELETED and rebuilt from the form.</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>Item Details - an item whose type is Group Products points at a group; Quotation and Sales Order - picking a group brings its parts in; stock reports - the parts move, not the group.</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>A GROUP IS A RECIPE, NOT STOCK. There is no stock figure for a group and nothing reserves the parts. If one part is short, nothing warns you when the group is chosen.
+item_group_slno is MAX + 1 - the same race as every other code in BIE.
+company_id is a leftover from the Benzear fork; nothing reads it.
+Abandoning a half-built group leaves rows in the _temp table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="136.1538461538462" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Item Price History</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>mst_itemprice_history_list.php (list) &gt; mst_itemprice_history.php (THE PRICE CHANGE, 1,014 lines) &gt; inc/datatable/ajaxItemPriceHistoryList.php &gt; inc/cis_ajax/modal_update_items.php (last 10 changes, in a modal)</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Ledger groups; supplies ledger_type. Maintained in Accounts.</t>
+          <t>Log - AND THE ONLY SCREEN THAT CAN CHANGE A PRICE</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>2.1, 2.2, 3.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>tbl_dc_package_box</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>lookup</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Packing box types for delivery challans.</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>mst_state</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>lookup</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>States and GST state codes - drives CGST/SGST vs IGST.</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>mst_district</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>lookup</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Districts within a state.</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>mst_city</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>lookup</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Cities within a district.</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>2.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>mst_department</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>lookup</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Departments. Status column is rec_del_status.</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>2.7, 3.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>mst_designation</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>lookup</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Job titles within a department.</t>
-        </is>
-      </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>2.8, 3.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>tbl_month_master</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>setup</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Per month: total days, WORKING DAYS, holidays, function holidays. The payroll divisor.</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>2.9, and all four attendance reports</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>mst_finyear</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>setup</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>Financial years. Serials restart within each; the active year goes into supplier and advance codes.</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>2.2, 3.7, 3.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>mst_employee</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>master</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>~65</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>The employee record. bio_id is the link to imported attendance; emp_type 1 Staff / 2 Labour / 3 Others.</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>3.1-3.3, 3.6-3.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>mst_employee_certificate</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>child</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>Uploaded certificates per employee. STAFF ONLY - the insert is guarded by emp_type == 1.</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>tbl_asset_details</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>child</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Company assets issued to an employee. Rebuilt on every edit.</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>mst_labour</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>lookup</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>Labour groups or contractors. Still carries an unused company_id from the Benzear fork.</t>
-        </is>
-      </c>
-      <c r="E27" s="10" t="inlineStr">
-        <is>
-          <t>3.4, 3.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>mst_salary_setting</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>master</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>Salary packages. Every component is decimal(6,2) - max 9999.99.</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>tbl_emp_advance</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>transaction</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>Advances paid to employees, with running balance. advance_status 3 = treated as settled.</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>3.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>tbl_emp_advance_return_payment</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>transaction</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>Recoveries against an advance, tagged with the attendance month and year.</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>3.7, attendance reports</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>tbl_emp_debit_note</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>transaction</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>Charges raised against employees.</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>tbl_accounts</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>journal</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>THE CENTRAL DOUBLE-ENTRY JOURNAL. Every money movement posts here; Day Book, Ledger Book and Trial Balance are three readings of it.</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>3.7, 3.8 (and most of the system)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>mst_shifts</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>setup</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>The two shifts and the six clock times that define each. Turns a punch into a present, a late or an overtime.</t>
-        </is>
-      </c>
-      <c r="E33" s="10" t="inlineStr">
-        <is>
-          <t>3.9, Import Attendance, all attendance reports</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>tbl_item_stock</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>stock</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>many</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>One row per item, with a BLOCK OF COLUMNS PER BRANCH. Not written in Phase 1, but mst_branch is entirely about it.</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>(Phase 2)</t>
+          <t>The menu item is a LOG: every price change ever made, with the old and new figures side by side. The screen behind it, reached from the Item Details list, is where a price is ACTUALLY CHANGED - because editing an item does not change its price. A change works on ONE BRANCH AT A TIME: yours.</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>tbl_itemprice_history (W - one row per change, itself organised by branch)
+tbl_item_stock (W - overwritten with the new figures)
+tbl_item_details (W - item_uom and item_hsn only)
+tbl_multiuom_itemprice_history (W)
+mst_branch (R - your branch's column names)
+mst_uom / mst_hsn (R)</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>INSERT tbl_itemprice_history - ONE ROW holding BOTH sets of figures: the new ones in &lt;branch&gt;_new_price, _discount, _min_discount, _max_discount, _cost_price, _selling_price, _margin, _msq, _maq, _moq, _item_uom, _item_hsn; the superseded ones in the matching &lt;branch&gt;_old_* columns.
+UPDATE tbl_item_details SET item_uom, item_hsn.
+UPDATE tbl_item_stock SET &lt;branch&gt;_item_price, _discount, _min_discount, _max_discount, _cost_price, _selling_price, _margin, _msq, _maq, _moq AND &lt;branch&gt;_stock - see traps.
+INSERT tbl_multiuom_itemprice_history for multi-UOM items.</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>1. From the Item Details list click the Item Price Update icon on the item's row.
+2. The screen loads YOUR BRANCH's current figures by reading the column names from mst_branch and selecting them under generic aliases.
+3. Enter the NEW figures. You may also change the UOM and the HSN here.
+4. Save - one history row carrying both sets, then item_uom / item_hsn, then the current columns are overwritten.
+5. To see the history: Item Masters &gt; Item Price History for the full log, or the price modal on the item list for that item's last ten changes.</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Quotation and Invoice - the new price is offered from the next line you add; Item Details list - the current price column; Item Price History; the price modal; Cost Worksheet and the margin reports.</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>THIS SCREEN ALSO WRITES THE STOCK QUANTITY. The same UPDATE sets &lt;branch&gt;_stock from a form field named branch_stock_field - an ORDINARY EDITABLE TEXT BOX that the page fills with the current stock when it loads (its placeholder still reads 'Enter MAQ'). So (a) anyone changing a price can type over the stock, and (b) even untouched, the value saved is whatever the stock was WHEN THE PAGE OPENED - a GRN or invoice posted meanwhile is silently wiped. DO NOT LEAVE THIS SCREEN OPEN.
+A PRICE CHANGE IS PER BRANCH AND DOES NOT PROPAGATE - the three branches start identical (from the item form) and then drift apart silently.
+created_by and created_dtm come from $_REQUEST, not from the session and the clock.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:E34"/>
+  <autoFilter ref="A5:J15"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -4719,30 +7662,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Coverage tracker</t>
+          <t>Menu 5  ·  Attendance and Salary  (mm_id = 24)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Menu order follows the sidebar. Update the Status column as each phase lands - the totals below recalculate.</t>
+          <t>5 screens. One imports punches, two calculate and pay, two report. Six things must be in place first: the employee and their bio_id, their CTC, their salary package, the month's working days, the punches, and the payment. Nothing is frozen until Issue Salary is pressed.</t>
         </is>
       </c>
     </row>
@@ -4750,494 +7695,855 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Order</t>
+          <t>#</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Main menu</t>
+          <t>Sub-menu (form)</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>mm_id</t>
+          <t>PHP file(s)</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Screens</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Word part</t>
+          <t>What it does (short)</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Phase</t>
+          <t>Tables used</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>What changes in the tables</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="n">
-        <v>1</v>
+          <t>Full flow</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Where it reflects</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Key notes / traps</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="152.8846153846154" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Settings</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>3</v>
+          <t>Attendance Update (Import Attendance)</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>import_attendance.php (605 lines); also attendance_new.php, attendance_report.php</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Import - a two-stage batch</t>
+        </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Part 1</t>
+          <t>Upload the biometric machine's Excel export. The screen matches each punch to an employee, pairs punches into a check-in and a check-out per day, and works out how long each person was there.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>tbl_attendance_import_new (RW - stage one, one row per raw punch)
+tbl_attendance (RW - stage two, one row per employee per work date)
+mst_employee (R - bio_id to emp_id)
+mst_shifts (R - only check_in and check_out)</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>STAGE ONE: DELETE FROM tbl_attendance_import_new WHERE same bio_id AND same biometric_time; DELETE FROM tbl_attendance WHERE same bio_id AND same work_date (so a re-import REPLACES rather than doubles); INSERT the punch with sync_status = 0.
+STAGE TWO: UPDATE tbl_attendance_import_new SET sync_status = 1, check_in_out (IN/OUT), shift_id; INSERT tbl_attendance on the first IN of a date; UPDATE its check_out when the closing punch is found.
+STAGE THREE: for every day with both punches and work_time = 0, UPDATE tbl_attendance SET work_time, break_time, late_in, late_out, early_in, early_out (all in MINUTES).</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Administrators only. One menu item has no file behind it</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="n">
-        <v>2</v>
+          <t>1. Attendance and Salary &gt; Attendance Update; choose the machine's Excel file.
+2. Column 4 of each row is the bio_id; the employee is looked up by it.
+3. The raw punches go in untouched, so a disputed day can be traced back to the machine readings.
+4. The unprocessed punches are walked in order; each is marked the OPPOSITE of the one before it.
+5. Work minutes are the sum of the in-to-out stretches; break minutes are the gaps.
+6. Finally the shift row is read and late_in / early_in are measured against check_in, late_out / early_out against check_out.
+7. Open Attendance Report to see the result and correct a day by hand if the machine missed a punch.</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Attendance Report (PF) and (Without PF) - days present, and therefore pay; OT Report - work_time beyond the normal day; Attendance Report - the day-by-day view.</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>EVERYONE IS IMPORTED AS DAY SHIFT: the code sets shift_id = 1 for every punch; the shift is never chosen. A night worker punching in at 19:00 is measured against DAY's 09:00 start and comes out ~10 hours late every day. The NIGHT row in mst_shifts exists and is never used.
+AN EMPLOYEE WITH NO bio_id IS INVISIBLE TO PAYROLL - the lookup is by bio_id alone and the reports select WHERE bio_id &gt; 0. Someone with it blank has no attendance and is silently not paid. Two employees sharing a bio_id share punches.
+IN AND OUT ARE INFERRED, NOT READ - a punch is marked the opposite of the one before it, so a single missed punch flips every punch after it for that person.
+RE-IMPORTING IS SAFE and is the right first move: both the raw punch and the day record are deleted before being written again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="181.1538461538462" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Masters</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>9</v>
+          <t>Employee Salary Report - PF</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>attendance_report_pf.php (667 lines) &gt; issue_salary.php (the Issue Salary action) &gt; checkattendance.php &gt; emp_advance_return_payment.php &gt; emp_debit_return_payment.php</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>THE PAYROLL RUN - report on screen, payment on a button</t>
+        </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>Part 2</t>
+          <t>Pick a month and year and you get the payroll for employees with emp_pf = 2: days worked, earned pay broken into components, EPF, recoveries against advances and debit notes, and the net. Issue Salary is the payment.</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>Done</t>
+          <t>mst_employee (R - bio_id &gt; 0, rec_del_status = 1, emp_pf = 2)
+tbl_attendance (R - days present)
+tbl_month_master (R - working_days, total_days, function_holidays)
+tbl_emp_salary (R - em_current = 1: CTC and package)
+mst_salary_setting (R - the percentages)
+tbl_emp_advance + tbl_emp_advance_return_payment (RW)
+tbl_emp_debit_note + tbl_emp_debit_note_return_payment (RW)
+tbl_emp_monthly_salary (W - the frozen payslip)
+tbl_accounts (W - the journal entry)</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>THE CALCULATION:
+  earned = CTC / working_days x paid_days   (sal_period = 2, monthly)
+  earned = CTC x paid_days                  (otherwise, daily)
+  basic = earned x sal_basic%; da, hra, conveyance the same
+  EPF   = (basic + da) x sal_pf%
+  net   = earned - EPF - advance recovered - debit recovered
+ADVANCE (+): INSERT tbl_emp_advance_return_payment (with atten_month, atten_year); UPDATE tbl_emp_advance SET return_amount up, balance_amount down, advance_status = 3.
+DEBIT (+): the same on the debit note tables.
+ISSUE SALARY: INSERT tbl_emp_monthly_salary (salary_for, total_working_days, paid_days, work_days, emp_ctc, earned_salary, basic_salary, da_salary, basic_da, hra_salary, convay_salary, epf_amount, both recoveries, net_amount, salary_type = 'WPF', salary_status = 1, issued_by, issued_dtm); INSERT tbl_accounts (voucher_type = 'Employee Salary', acc_tran_value = net, dr_ledger_id = 1, cr_ledger_id = the employee's ledger).</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>Month Master is the payroll calendar, not a lookup</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>3</v>
+          <t>1. Choose the MONTH and YEAR. The month list comes from Month Master, so a month with no row cannot be selected.
+2. The screen builds every row from live master data.
+3. PAID DAYS ARE CAPPED AT WORKING DAYS - extra days present do not raise the pay.
+4. Recover an advance with the (+) in the advance column; emp_advance_return_payment.php opens knowing the employee, month, year and net pay.
+5. Recover a debit note the same way.
+6. Check the net column, then press ISSUE SALARY.
+7. The Issue button disappears for that employee and month - the screen looks for an existing issued row before drawing it.</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>EPF Report - reads the issued WPF rows; nothing appears there until salary is issued. Day Book, Ledger Book, Trial Balance via tbl_accounts. The employee's ledger. Employee Advance and Employee Debit Note - balances fall.</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>NOTHING IS FROZEN UNTIL YOU PRESS ISSUE SALARY. Every figure is recalculated from live master data each time the report opens, so changing a CTC, a package percentage or a working-days count changes LAST MONTH's report too - until that month is issued.
+issue_salary.php TRUSTS EVERYTHING THE BROWSER SENDS IT: every figure is calculated while the page renders, written into hidden fields, and posted straight into the payslip and the journal. Nothing is recalculated server-side, and the endpoint has NO DUPLICATE CHECK - the hidden button is the only guard.
+THE SALARY EXPENSE LEDGER IS HARDCODED AS LEDGER ID 1 (dr_ledger_id = 1). Check what ledger 1 actually is before the first run.
+A PART-RECOVERY MARKS AN ADVANCE SETTLED (advance_status = 3), and next month's report reads outstanding with advance_status != 3 - so an advance recovered in instalments drops out after the first one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="64" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>HR Management</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>9</v>
+          <t>Employee Salary Report - WPF (Without PF)</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>attendance_report_withoutpf.php (701 lines) &gt; issue_salary.php &gt; checkattendance.php &gt; emp_advance_return_payment.php &gt; emp_debit_return_payment.php</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>THE PAYROLL RUN - the non-PF half</t>
+        </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Part 3</t>
+          <t>Identical to 5.2 in every way except two: it lists employees whose emp_pf is NOT 2, and it does not deduct EPF. Same calculation, same Issue Salary button, same journal entry.</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="n">
-        <v>4</v>
+          <t>Exactly as 5.2, except mst_employee is filtered the other way and epf_amount is not deducted.</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>As 5.2, but salary_type = 'WOPF' on the tbl_emp_monthly_salary row and no EPF deduction in the net.</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>As 5.2.</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>Day Book, Ledger Book, Trial Balance; the employee's ledger; Employee Advance and Debit Note. NOT the EPF Report, which reads WPF rows only.</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>All of 5.2's traps apply here too - the two screens are built from the same code.
+An employee on the wrong side of emp_pf appears on the wrong report and is paid with or without EPF accordingly. emp_pf = 2 means PF; anything else means no PF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="90.19230769230769" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Item Masters</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>10</v>
+          <t>Employee Salary Report - OT</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>attendance_report_ot.php (454 lines) &gt; issue_salary.php</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>The overtime run - a SECOND, SEPARATE payment</t>
+        </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>Part 4</t>
+          <t>Overtime is paid separately from salary, on its own run, against its own rate. Eligible: Labour employees (emp_type = 2) PLUS anyone whose current salary revision has emp_ot_sal &gt; 0 - and of those, only people with attendance in the month.</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>Phase 2</t>
-        </is>
-      </c>
-      <c r="G9" s="15" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>5</v>
+          <t>mst_employee (R - the eligibility filter)
+tbl_attendance (R - work_time and the is_ot flag)
+tbl_emp_salary (R - emp_ot_sal from the current revision)
+tbl_emp_monthly_salary (W)
+tbl_accounts (W)</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>INSERT tbl_emp_monthly_salary (salary_for, total_ot_hours, amount_per_hour, ot_amount, tiffen_allow_days, tiffen_amount, total_ot_amount, salary_type = 'OT', salary_status = 1, issued_by, issued_dtm).
+INSERT tbl_accounts - a SECOND journal entry for the same employee and month, separate from their salary.</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>1. Choose the MONTH and YEAR.
+2. For each eligible employee the screen walks their attendance days and accumulates overtime minutes from work_time, taking is_ot into account.
+3. The total is kept in MINUTES and divided out into hours and minutes for display.
+4. The rate comes from emp_ot_sal on the current salary revision. Tiffin allowance days and amount can be added.
+5. Press Issue Salary - the same endpoint, but salary_type = 'OT' and only the OT columns filled.</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Day Book, Ledger Book, Trial Balance; the employee's ledger - a second credit for the month; tbl_emp_monthly_salary - two rows for the month, one WPF/WOPF and one OT.</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>AN EMPLOYEE CAN BE PAID TWICE FOR THE SAME MONTH - once on the salary run and once here - and that is intended. When reconciling a month's payroll, sum both.
+ELIGIBILITY IS EASY TO GET WRONG: a Staff employee is only listed if their CURRENT salary revision has emp_ot_sal &gt; 0. Set it to zero, or forget it on a new revision, and they silently vanish even though the attendance shows the hours.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="96.92307692307692" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Attendance and Salary</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>5</v>
+          <t>Employee Salary Report - EPF</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>attendance_report_epf.php (421 lines) &gt; attendance_report_epf_txt.php (the upload file)</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Statutory report - READ ONLY</t>
+        </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Part 5</t>
+          <t>The provident fund return for a month in the shape the EPFO wants: each member with their EPF number and UAN, their wages, and the contribution split into EPS and EDLI. A second button produces the same data as a text file for the EPFO portal.</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Phase 2</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>Part 6</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>Phase 2</t>
-        </is>
-      </c>
-      <c r="G11" s="15" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>Purchase</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>Part 7</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>Phase 2</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Stores</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="D13" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>Part 8</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>Phase 2</t>
-        </is>
-      </c>
-      <c r="G13" s="15" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>Where stock actually moves</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>Accounts</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>Part 9</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>Phase 3</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>Report</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="D15" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>Part 10</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>Phase 3</t>
-        </is>
-      </c>
-      <c r="G15" s="15" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>Largest menu - 14 reports</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>Part 11</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>Phase 3</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>Menus in the system</t>
-        </is>
-      </c>
-      <c r="C18" s="18">
-        <f>COUNTA(B6:B16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>Menus documented</t>
-        </is>
-      </c>
-      <c r="C19" s="18">
-        <f>COUNTIF(G6:G16,"Done")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>Screens in the system</t>
-        </is>
-      </c>
-      <c r="C20" s="18">
-        <f>SUM(D6:D16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>Screens documented</t>
-        </is>
-      </c>
-      <c r="C21" s="18">
-        <f>SUMIF(G6:G16,"Done",D6:D16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>Screens remaining</t>
-        </is>
-      </c>
-      <c r="C22" s="18">
-        <f>SUMIF(G6:G16,"Pending",D6:D16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>Percent complete</t>
-        </is>
-      </c>
-      <c r="C23" s="19">
-        <f>IFERROR(SUMIF(G6:G16,"Done",D6:D16)/SUM(D6:D16),0)</f>
-        <v/>
+          <t>tbl_emp_monthly_salary (R - issued rows with salary_type = 'WPF')
+mst_employee (R - emp_name, emp_epf_no, emp_uan_no)</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>NOTHING. This screen writes nothing at all.</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>1. Choose the MONTH and YEAR.
+2. The screen selects issued PF payslips: salary_for = '&lt;year&gt;-&lt;month&gt;', salary_type = 'WPF', salary_status = 1.
+3. For each it takes basic_da and epf_amount from the payslip and splits the contribution: EPS = basic_da x 8.33%, EDLI = epf_amount - EPS.
+4. EPF number and UAN come from the employee record.
+5. Print, or use the text-file button for attendance_report_epf_txt.php.</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Nothing inside BIE - the output goes to the EPFO portal.</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>NOTHING APPEARS HERE UNTIL SALARY IS ISSUED. The report reads issued payslips, not attendance. An employee whose salary has not been issued is simply absent from the return, with no warning.
+THE 8.33 PER CENT EPS RATE IS HARDCODED IN THE PAGE, as is the assumption that everything above it is EDLI, and NO WAGE CEILING is applied. A statutory change is a code change.
+A MISSING EPF NUMBER OR UAN IS NOT FLAGGED - the employee appears with empty columns and the text file is generated with the gaps in it.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="A22:B22"/>
-  </mergeCells>
+  <autoFilter ref="A5:J10"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menu 6  ·  Sales  (mm_id = 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2 menu items, a longer chain: quotation (versioned, verified then approved), sales order generated from it, delivery challan, invoice. STOCK DOES NOT MOVE UNTIL THE INVOICE - not on the quotation, not on the order, and not on the challan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Sub-menu (form)</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>PHP file(s)</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>What it does (short)</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Tables used</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>What changes in the tables</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Full flow</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Where it reflects</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Key notes / traps</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="177.3076923076923" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Quotation List</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>lst_quotation.php (list) &gt; quotation.php (add/edit, 2,234 lines) &gt; inc/datatable/ajaxQuotationlist.php &gt; print_quotation.php &gt; quo_proforma_invoice_print.php &gt; lst_quo_approval.php + inc/cis_ajax/jquery_quo_approval.php (approval) &gt; gen_so.php, quo_invoice.php (conversion)</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Transaction - VERSIONED, with a two-step approval</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>A priced offer: the customer, the items, the rates and discounts, the tax, and up to eight standard terms. Revising it does NOT overwrite - a new row is written with the same quo_slno, quo_version + 1, and prev_quo_id pointing back. Verified by one person and approved by another before it can be used.</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>tbl_quotation (RW)
+tbl_quotation_details (RW)
+tbl_quo_pack_details (RW)
+mst_supplier_new (R - the customer, and discount_apply)
+mst_customer_branch (R)
+tbl_item_details + tbl_item_stock (R - this branch's price and stock)
+mst_hsn (R)
+mst_finyear (R)
+tbl_task_user (R - the approver)</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>INSERT tbl_quotation (quo_slno, quo_version, quo_refno, prev_quo_id, supp_id, branch_id, quo_value, terms_con_id1..8, bie_branch_id).
+DELETE + INSERT tbl_quotation_details and tbl_quo_pack_details - rebuilt on every save.
+VERIFY: UPDATE quo_verify_status, quo_verify_by, quo_verify_date_time AND quo_approve_status BACK TO 0.
+APPROVE: UPDATE quo_approve_status, quo_approve_by, quo_approve_remarks, quo_approve_date_time.
+CONVERT: UPDATE so_gen_status + quo_so_id, or inv_gen_status + quo_inv_id.
+DELETE: UPDATE quo_status = 0.</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>1. Sales &gt; Quotation List - quotations for your branch with version, value and approval state.
+2. Add New; the serial is MAX(quo_slno) + 1 within the financial year, padded to three digits; version starts at 1.
+3. Choose the CUSTOMER and their BRANCH, the date, the contact phone and email to print.
+4. Add item lines. Picking an item returns YOUR BRANCH's price, discount and stock, plus the customer's discount_apply flag which decides whether the discount fills in automatically.
+5. Pick up to EIGHT terms and conditions, plus free-text terms.
+6. Save - header, lines, packing rows.
+7. VERIFY - someone sets quo_verify_status.
+8. APPROVE - the approver found from tbl_task_user approves or rejects with a remark.
+9. REVISE - editing writes a NEW row: same slno, version + 1, prev_quo_id set, BOTH STATUS FLAGS RESET TO 0.
+10. CONVERT - generate a sales order (gen_so.php) or go straight to an invoice (quo_invoice.php).</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Sales Order - generated from an approved quotation, which keeps quo_id; Invoice - through the SO and challan, or straight from here; Quotation Branch Report and Sales List; print_quotation.php on the branch letterhead; quo_proforma_invoice_print.php.</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>branch_id AND bie_branch_id MEAN OPPOSITE THINGS: branch_id is the CUSTOMER's delivery branch (mst_customer_branch), bie_branch_id is the BIE branch raising it (mst_branch). Getting them the wrong way round in a report produces plausible-looking nonsense.
+QUOTATION APPROVAL IS ROUTED TO THE WRONG TASK: tbl_task_user holds 1 PO Approval, 2 Supplier Approval, 3 Quotation Approval - but quotation.php looks up task_id = 1. Row 3 is never read. Both currently name user 1, so nothing looks wrong until you reassign.
+VERIFYING RESETS THE APPROVAL - approve last.
+STOCK DOES NOT MOVE HERE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="96.53846153846153" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Sales Order List</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>lst_sales_order.php (list) &gt; gen_so.php (generate/edit, 806 lines) &gt; inc/datatable/ajaxSaleslist.php &gt; print_sales_order.php &gt; inc/cis_ajax/jquery_modal_sales_det.php (view) &gt; inc/cis_ajax/jquery_modal_so_reject_reason.php (reject) &gt; dc_add.php, invoice_print.php</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Transaction - ALWAYS generated from a quotation</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>The customer has accepted. There is no blank sales order form: gen_so.php is reached from the quotation list and the quotation's lines are carried across.</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>tbl_sales_order (RW)
+tbl_sales_order_details (RW)
+tbl_sales_order_pack_dts (RW)
+tbl_quotation (R for the lines; W to record the conversion)
+mst_supplier_new + mst_customer_branch (R)
+tbl_item_details + tbl_item_stock (R)
+mst_finyear + mst_branch (R - both go into the reference)</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>INSERT tbl_sales_order (so_finyr, so_slno, so_refno, so_ref, so_date, despatch_date, quo_id, supp_id, branch_id, bie_branch_id, item_net_val, bal_value).
+DELETE + INSERT tbl_sales_order_details and tbl_sales_order_pack_dts.
+UPDATE tbl_quotation SET so_gen_status = 1, quo_so_id = the new order.
+UPDATE tbl_sales_order SET dc_status = 1 when a challan is raised.
+UPDATE tbl_sales_order on invoicing, by dc_invoice.php or quo_invoice.php.</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>1. From the Quotation List, open an APPROVED quotation and choose Generate SO.
+2. Enter the sales order number, the order date, the customer's own reference and the DESPATCH DATE.
+3. Adjust lines if the accepted order differs from the quotation.
+4. Save - the reference is built as SO/0042/BIE/&lt;branch&gt;/&lt;finyear&gt;, and the quotation is stamped so_gen_status = 1.
+5. From the list: view in a modal, print, REJECT with a reason, raise a DELIVERY CHALLAN (dc_add.php), or print the invoice once one exists.</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Delivery Challan - raised from this order; Invoice - through the challan; Sales Order Report and SO Stock List Branchwise; print_sales_order.php; the quotation, which now shows as converted.</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>A SALES ORDER COMMITS NOTHING - no stock is reserved and no quantity is set aside. Two orders can promise the same single unit and both look fine until one reaches the invoice. item_allotted_qty exists on tbl_item_details but NOTHING WRITES IT.
+dc_status IS A FLAG, NOT A COUNT: one challan against a ten-line order sets it to 1 and it never comes back.
+branch_id / bie_branch_id - the same trap as 6.1.
+STOCK DOES NOT MOVE HERE.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:J7"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menu 7  ·  Purchase  (mm_id = 19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2 screens, two routes to the same place. Either raise a purchase order directly, or let a store indent be priced up through PO Prepare. Both end at a purchase order waiting for goods, and both move no stock - the GRN does that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Sub-menu (form)</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>PHP file(s)</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>What it does (short)</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Tables used</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>What changes in the tables</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Full flow</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Where it reflects</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Key notes / traps</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="135.1923076923077" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Direct PO List</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>lst_direct_po.php (list) &gt; direct_purchase_order.php (add/edit, 1,306 lines) &gt; inc/datatable/ajaxPoList.php &gt; po_print.php &gt; grn_add.php, grn_view.php, supp_invoice_add.php</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Transaction with approval</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>A purchase order raised directly, without an indent: supplier, items, agreed rates, tax, delivery terms. ONLY APPROVED SUPPLIERS appear in the dropdown. The printed order draws its letterhead from YOUR branch's mst_branch row.</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>tbl_purchase_order (RW)
+tbl_purchase_order_details (RW)
+tbl_po_print_details (RW)
+mst_supplier_new (R - supp_approve_status = 1 only)
+tbl_item_details + tbl_item_stock (R)
+mst_hsn (R)
+mst_finyear + mst_branch (R)
+tbl_task_user (R - task_id = 1)</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>INSERT tbl_purchase_order (po_finyr, po_slno, po_refno, po_date, supp_id, branch_id, value, po_approve_id from tbl_task_user).
+DELETE + INSERT tbl_purchase_order_details and tbl_po_print_details.
+UPDATE tbl_purchase_order on approve - flag, approver, timestamp.
+UPDATE tbl_purchase_order by GRN - to record receipt.
+DELETE: status to 0.</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>1. Purchase &gt; Direct PO List - orders for your branch with their approval state.
+2. Add New; the serial is MAX(po_slno) + 1 WITHIN YOUR BRANCH; the reference is PO/0042/BIE/&lt;branch&gt;/&lt;finyear&gt;.
+3. Choose the SUPPLIER - unapproved suppliers are not offered.
+4. Add item lines: item, quantity, rate, discount. Tax comes from the item's HSN.
+5. Enter delivery terms, payment terms and printed notes - these go to tbl_po_print_details.
+6. Save. The approver is looked up from tbl_task_user and stored on the order.
+7. APPROVE - until then goods cannot be received against it.
+8. From the list: print, raise a GRN (grn_add.php), view a GRN (grn_view.php), or record the supplier's bill (supp_invoice_add.php).</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>GRN - raised against this order; this is where stock increases. GRN Payment Details - what is owed. Cost Worksheet. po_print.php on your branch's letterhead. The supplier's ledger once the bill is recorded.</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>THE ORDER NUMBER IS MAX + 1 COMPUTED BEFORE THE INSERT - two buyers at the same branch saving simultaneously get the same po_slno and the same printed reference.
+THE APPROVER IS FROZEN ONTO THE ORDER at creation (po_approve_id). Change who approves POs and every order already raised still waits for the old approver.
+Supplier approval is not re-checked on save - only when the dropdown is drawn.
+STOCK DOES NOT MOVE HERE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="124.6153846153846" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>PO Prepare List</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>po_prepare_list.php (list) &gt; po_prepare.php (prepare, 1,077 lines) &gt; inc/datatable/ajaxPoPrepareList.php &gt; po_prepare_print.php &gt; store_indent_add.php, store_indent_print.php</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>The pricing step between an indent and an order</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>A store indent says what is needed but carries no prices and names no supplier. This screen puts A SUPPLIER AND A PRICE AGAINST EVERY LINE. Lines are handled individually, each with its own supp_id, rate, discount, tax and item_prepare_status - so half an indent can be priced today, and different lines can go to different suppliers.</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>tbl_po_prepare (RW)
+tbl_po_prepare_dets (RW - one row per line, each with its own supplier)
+tbl_store_indent + tbl_store_indent_details (R)
+mst_supplier_new (R - approved, per line)
+tbl_item_details + tbl_item_stock (R)
+mst_hsn (R)
+mst_finyear (R)</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>INSERT tbl_po_prepare (po_prepare_date, po_prepare_finyr, si_id, remarks, send_to_admin_status).
+DELETE FROM tbl_po_prepare_dets WHERE po_prepare_id = &lt;this sheet&gt;.
+INSERT tbl_po_prepare_dets - one row per line: si_id, supp_id, item_id, si_qty, uom, item_discount, unit_price, price, gst, gst_id, net_amt, item_prepare_status.
+UPDATE tbl_po_prepare on re-save, including send_to_admin_status.</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>1. Purchase &gt; PO Prepare List - indents waiting to be priced, and ones in progress.
+2. Open one; po_prepare.php shows the indent's lines with quantity and current stock.
+3. For EACH LINE choose the supplier, enter unit price and discount, confirm UOM and tax; the net is worked out.
+4. Lines not yet dealt with keep their item_prepare_status, so you can come back.
+5. Set SEND TO ADMIN when the sheet is ready.
+6. Save - header written or updated, detail rows DELETED AND REBUILT from the form.
+7. Print with po_prepare_print.php, or open the source indent with store_indent_print.php.
+8. Administration raises the purchase order or orders from it.</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Direct PO / Purchase Order - the priced lines become one or more orders; Store Indent List - the indent shows as being worked on; po_prepare_print.php; Cost Worksheet.</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>EVERY SAVE REBUILDS ALL THE LINES - if a line is not on the form when you save, it is gone, and with it the supplier and price already chosen. Check the line count after saving a long sheet.
+NOTHING LINKS THE RESULTING PURCHASE ORDER BACK TO THIS SHEET - tbl_purchase_order has no po_prepare_id. The chain is traceable forwards but not backwards.
+An unpriced line is not blocked - it can be saved and sent to admin; it simply cannot be ordered.
+company_id is a Benzear-fork leftover.
+STOCK DOES NOT MOVE HERE.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:J7"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/BIE_ERP_Documentation.xlsx
+++ b/docs/BIE_ERP_Documentation.xlsx
@@ -17,8 +17,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. Sales" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. Purchase" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. Stores" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables Reference" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. Accounts" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. Report" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11. Service" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables Reference" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Menu Index'!$A$5:$F$79</definedName>
@@ -39,9 +42,15 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'7. Purchase'!$5:$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'8. Stores'!$A$5:$J$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'8. Stores'!$5:$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Tables Reference'!$A$5:$E$79</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Tables Reference'!$5:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="11">'Coverage'!$5:$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'9. Accounts'!$A$5:$J$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'9. Accounts'!$5:$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'10. Report'!$A$5:$J$19</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'10. Report'!$5:$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'11. Service'!$A$5:$J$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'11. Service'!$5:$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Tables Reference'!$A$5:$E$94</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'Tables Reference'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'Coverage'!$5:$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -52,7 +61,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -118,12 +127,6 @@
       <color rgb="000F6E52"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="005B6470"/>
-      <sz val="9"/>
-    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -174,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -212,12 +215,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -592,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -609,7 +606,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Phase 1  ·  Settings, Masters and HR Management  ·  21 of 63 screens  ·  companion to the Word document</t>
+          <t>Complete  ·  all 11 menus, all 63 screens  ·  companion to the Word document</t>
         </is>
       </c>
     </row>
@@ -622,7 +619,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>One row per screen, one sheet per menu. The same material as the Word document, laid out for quick lookup and for tracking coverage as later phases are added.</t>
+          <t>One row per screen, one sheet per menu, covering all 63 live screens. The same material as the Word document, laid out for quick lookup rather than for reading straight through.</t>
         </is>
       </c>
     </row>
@@ -761,338 +758,434 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Tables Reference</t>
+          <t>9. Accounts</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Every table touched in this phase, what it holds, and which screens use it.</t>
+          <t>3 screens - the invoice, money in from customers, money out to suppliers. Read 9.1 first.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>10. Report</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>14 reports, every one read-only. Six on stock, five on sales, one each on cost, discounts and quotations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>11. Service</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>2 screens - which spares fit which product, and repairs booked against an invoice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Tables Reference</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Every table the live menu touches - 89 of them - what it holds, and which screens use it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
           <t>Coverage</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Phase plan and progress, with live formulas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="12" customHeight="1">
-      <c r="A20" s="3" t="inlineStr"/>
-      <c r="B20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21" ht="12" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>All 11 menus, complete, with live formulas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="12" customHeight="1">
+      <c r="A23" s="3" t="inlineStr"/>
+      <c r="B23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24" ht="12" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>THE ONE THING TO UNDERSTAND FIRST</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr"/>
-    </row>
-    <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>BIE is multi-BRANCH by COLUMN</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Most systems add a branch_id column and store one row per branch. BIE does not. It stores ONE ROW PER ITEM and gives each branch its own SET OF COLUMNS - ho_stock, kl_stock, rjpm_stock, and the same again for every price, discount, margin and bin location.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="42" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>mst_branch stores the names</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>The branch row does not hold the stock; it holds the NAME OF THE COLUMN that holds the stock. A screen reads branch_stock_field from mst_branch, gets back the text 'ho_stock', and builds its SQL around it. That substitution is every branch-aware query in BIE.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Why it matters</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>When a figure looks right for one branch and wrong for another, this is why - the two branches are literally different columns, and a screen that hardcodes ho_stock is right at Head Office and wrong everywhere else.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="12" customHeight="1">
-      <c r="A25" s="3" t="inlineStr"/>
-      <c r="B25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26" ht="12" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="28" ht="12" customHeight="1">
+      <c r="A28" s="3" t="inlineStr"/>
+      <c r="B28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29" ht="12" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>LEGEND</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr"/>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>R / W / RW</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Table is Read / Written / both by that screen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Soft delete</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>The dustbin icon sets a status column to 0 via inc/cis_ajax/jquery_delete_records.php (or jquery_delete_records_hr.php for HR). Nothing is physically removed, and lists filter on status = 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>(W) on mst_ledger</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>The screen auto-creates an accounts ledger BEFORE writing the master row, and stores its ledger_id on the master.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>tbl_accounts</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>The single central double-entry journal. Every money movement in the system posts here; Day Book, Ledger Book and Trial Balance are three readings of it.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>_temp tables</t>
+          <t>Soft delete</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Session-tagged staging for document lines while a form is open. Copied to the real table on save, then cleared.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="12" customHeight="1">
-      <c r="A32" s="3" t="inlineStr"/>
-      <c r="B32" s="4" t="inlineStr"/>
-    </row>
-    <row r="33" ht="12" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>FIVE RULES THAT HOLD NEARLY EVERYWHERE</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr"/>
+          <t>The dustbin icon sets a status column to 0 via inc/cis_ajax/jquery_delete_records.php (or jquery_delete_records_hr.php for HR). Nothing is physically removed, and lists filter on status = 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>(W) on mst_ledger</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>The screen auto-creates an accounts ledger BEFORE writing the master row, and stores its ledger_id on the master.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>tbl_accounts</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Looks like a central journal, and is WRITE-ONLY. Four payroll files insert into it and nothing anywhere reads it. BIE has no Day Book, no Ledger Book and no Trial Balance - see sheet 9, section 9.1.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>1. Nothing is really deleted</t>
+          <t>_temp tables</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Every master carries a status column; deleting sets it to 0. The one exception is tbl_user_rights, which is hard-deleted and rebuilt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>2. Customers and suppliers share a table</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Both are rows in mst_supplier_new - note the _new. supp_type: C = customer, S = supplier. There is no customer table.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>3. A party or an employee is also a ledger</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Customer, supplier and employee masters INSERT their mst_ledger row FIRST, then store the new ledger_id on the master row.</t>
-        </is>
-      </c>
+          <t>Session-tagged staging for document lines while a form is open. Copied to the real table on save, then cleared.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="12" customHeight="1">
+      <c r="A35" s="3" t="inlineStr"/>
+      <c r="B35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36" ht="12" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>FIVE RULES THAT HOLD NEARLY EVERYWHERE</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr"/>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
+          <t>1. Nothing is really deleted</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Every master carries a status column; deleting sets it to 0. The one exception is tbl_user_rights, which is hard-deleted and rebuilt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>2. Customers and suppliers share a table</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Both are rows in mst_supplier_new - note the _new. supp_type: C = customer, S = supplier. There is no customer table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>3. A party or an employee is also a ledger</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Customer, supplier and employee masters INSERT their mst_ledger row FIRST, then store the new ledger_id on the master row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
           <t>4. Documents with lines use a _temp staging table</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Lines are staged against your session id while you type, copied under the new header id on save, then cleared. Abandoned documents leave harmless orphan rows.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="42" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="41" ht="42" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>5. Most forms write themselves</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Few screens contain a hand-written INSERT. CIS_InsertRecord and CIS_UpdateRecord DESCRIBE the table and keep only posted values whose NAME MATCHES A REAL COLUMN. So the name of the input box IS the name of the column - and a typo is silently dropped.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="12" customHeight="1">
-      <c r="A39" s="3" t="inlineStr"/>
-      <c r="B39" s="4" t="inlineStr"/>
-    </row>
-    <row r="40" ht="12" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="42" ht="12" customHeight="1">
+      <c r="A42" s="3" t="inlineStr"/>
+      <c r="B42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43" ht="12" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>SCOPE</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr"/>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>Schema source</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>db/bie.sql - the current dump in the repository. 105 tables.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>Included</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Only files the live menu actually opens - 63 screens across 11 menus.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>Excluded</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>Eight mst_sub_menu rows with no URL. Seven are hidden; one, Bank Account Details under Settings, is set to show but goes nowhere.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>Field detail</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>The fields that DRIVE behaviour, plus every table write in full. Not an exhaustive inventory of every input on every form.</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="12" customHeight="1">
-      <c r="A45" s="3" t="inlineStr"/>
-      <c r="B45" s="4" t="inlineStr"/>
-    </row>
-    <row r="46" ht="12" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="48" ht="12" customHeight="1">
+      <c r="A48" s="3" t="inlineStr"/>
+      <c r="B48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49" ht="12" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>WHAT ACTUALLY MOVES STOCK</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr"/>
-    </row>
-    <row r="47" ht="42" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr"/>
+    </row>
+    <row r="50" ht="42" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>Only four screens change it</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>GRN (grn_add.php) puts stock UP. The three invoice screens - quo_invoice.php, dc_invoice.php, mng_invoice.php - put it DOWN. Nothing else in BIE touches tbl_item_stock's quantity columns, with one exception: Item Price Update writes the stock column too (see 4.10).</t>
         </is>
       </c>
-    </row>
-    <row r="48" ht="42" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Two gaps, not design</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>A DELIVERY CHALLAN takes goods out of the building and only the later invoice reduces stock, so anything despatched but not invoiced is counted twice. A PURCHASE RETURN sends goods back and NOTHING reduces stock at all, so the quantity stays up permanently.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="42" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>When a figure is wrong</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Check in this order: (1) challans raised but not invoiced, (2) purchase returns, (3) a price change made through Item Price Update, (4) whether you are reading tbl_item_details.item_curr_stock (stale) instead of the branch column on tbl_item_stock (live).</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="12" customHeight="1">
-      <c r="A50" s="3" t="inlineStr"/>
-      <c r="B50" s="4" t="inlineStr"/>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
+          <t>A third and fourth gap</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>REPAIR INDENT consumes parts and moves no stock either (11.2). And the price-update screen writes the stock column from a form field, so a price change can silently reset a quantity (4.10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="42" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Two gaps, not design</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>A DELIVERY CHALLAN takes goods out of the building and only the later invoice reduces stock, so anything despatched but not invoiced is counted twice. A PURCHASE RETURN sends goods back and NOTHING reduces stock at all, so the quantity stays up permanently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="42" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>When a figure is wrong</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Check in this order: (1) challans raised but not invoiced, (2) purchase returns, (3) repair indents, (4) a price change made through Item Price Update, (5) whether you are reading tbl_item_details.item_curr_stock (stale) instead of the branch column on tbl_item_stock (live).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="12" customHeight="1">
+      <c r="A54" s="3" t="inlineStr"/>
+      <c r="B54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55" ht="12" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>THERE IS NO GENERAL LEDGER</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr"/>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>What you might expect</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>A Day Book, a Ledger Book, a Trial Balance, customer and supplier balances. BIE has none of them - no such screen exists, in the menu or as an unlinked file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="42" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>What is actually there</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Money is tracked PER DOCUMENT. What a customer owes is tbl_invoice.inv_bal_value, reduced by credit payments and summed by the Credit List. What you owe a supplier is the GRN value less its payments, on GRN Payment Details. Nothing totals either by party.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>The trap</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>SALES RECEIPT records money against the SALES ORDER and never touches the invoice, while the Credit List reads only invoice credit payments. Use both screens and you double-count. Pick one route per customer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="12" customHeight="1">
+      <c r="A59" s="3" t="inlineStr"/>
+      <c r="B59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
           <t>Related system</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>Benzear is the sister codebase this one was forked from. Benzear is multi-COMPANY and keys on company_id; BIE is multi-BRANCH and keys on branch_id. A few unused company_id columns survive in BIE from that fork.</t>
         </is>
@@ -1488,7 +1581,1411 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menu 9  ·  Accounts  (mm_id = 21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>3 screens: the invoice - the step that reduces stock - money in from customers, and money out to suppliers. Read the README's 'There is no general ledger' section first: tbl_accounts is write-only, and money is tracked per document rather than per party.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Sub-menu (form)</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>PHP file(s)</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>What it does (short)</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Tables used</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>What changes in the tables</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Full flow</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Where it reflects</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Key notes / traps</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="167.3076923076923" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Invoice List</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>invoice_list.php (list) &gt; mng_invoice.php (direct, 1,672 lines) &gt; quo_invoice.php (from a quotation, 1,447) &gt; dc_invoice.php (from a challan, 1,457) &gt; mng_credit.php (credit payment, 749) &gt; inc/datatable/ajaxInvoiceList.php &gt; invoice_print.php, quo_invoice_print.php</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>TRANSACTION - THE STEP THAT REDUCES STOCK</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>The invoice. One list, but THREE screens write into it depending on where the invoice came from, setting invoice_type so you can tell them apart. End of the sales chain and the only place stock comes down. A CREDIT invoice leaves a balance on inv_bal_value, paid off later through mng_credit.php. Cash invoices can record a denomination breakdown.</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>tbl_invoice (RW)
+tbl_invoice_details (RW)
+tbl_invoice_pack_details (RW)
+tbl_invoice_denomination_details (RW)
+tbl_invoice_credit_details (W - one row per part-payment)
+tbl_item_stock (W - &lt;branch&gt;_stock REDUCED)
+tbl_stock_flow (W - trans_type 'INV')
+tbl_quotation / tbl_sales_order / tbl_dc (W - stamped as invoiced)
+mst_branch (R - the column name AND the print letterhead)
+mst_supplier_new, mst_customer_branch, mst_hsn (R)</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>INSERT tbl_invoice (inv_slno, inv_finyr, inv_refno, inv_date, quo_id, so_id, dc_id, supp_id, branch_id, inv_tot_value, inv_bal_value, invoice_type, credit_amount, credit_due_date).
+DELETE + INSERT tbl_invoice_details, tbl_invoice_pack_details, tbl_invoice_denomination_details.
+PER LINE: read branch_stock_field from mst_branch; INSERT tbl_stock_flow (trans_type = 'INV'); RE-READ the current stock from the database; UPDATE tbl_item_stock SET &lt;branch_stock_field&gt; = current - invoiced.
+UPDATE tbl_quotation / tbl_sales_order / tbl_dc - stamped as invoiced.
+CREDIT PAYMENT (mng_credit.php): INSERT tbl_invoice_credit_details (inv_id, paid_amount, paid_date, mode, reference); UPDATE tbl_invoice SET inv_bal_value = inv_bal_value - paid.
+NO tbl_accounts ENTRY.</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>1. Accounts &gt; Invoice List - invoices for your branch with type, value and balance.
+2. THREE WAYS IN: Direct (Add New -&gt; mng_invoice.php, invoice_type 'I'); from a quotation (Quotation List -&gt; quo_invoice.php, type 'Q'); from a challan (DC List -&gt; dc_invoice.php, type 'D').
+3. The reference is INV/0042/BIE/&lt;branch&gt;/&lt;finyear&gt;; the serial is MAX + 1 within your branch AND financial year.
+4. Enter or confirm lines, transport details, vehicle number, transport charge.
+5. Choose how it is paid. CASH allows a denomination breakdown. CREDIT sets a credit amount, due date and remark, leaving inv_bal_value outstanding.
+6. Save - header, lines, packing and denomination rows, then the per-line stock block.
+7. The source document is stamped so it cannot be invoiced twice.
+8. LATER, for a credit invoice: mng_credit.php records each part-payment and reduces inv_bal_value.</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Every stock figure in the system; Item Stock History via tbl_stock_flow; Credit List (invoices with inv_bal_value outstanding); Sales List and Invoice Report; the quotation, order or challan it came from; invoice_print.php on your branch's letterhead.</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>THE STOCK DEDUCTION IS SOUND - like the GRN it re-reads the current quantity from the database before subtracting, so concurrent invoices both land.
+NOTHING STOPS AN INVOICE GOING NEGATIVE - there is no check that current stock is large enough, and the sales order reserved nothing and the challan moved nothing.
+THREE SCREENS, ONE TABLE, AND THEY HAVE DRIFTED - mng_invoice, quo_invoice and dc_invoice are three copies of ~1,500 lines that do not do identical things. Change invoicing behaviour in all three.
+THE INVOICE POSTS NOTHING TO tbl_accounts. No revenue entry, no receivable entry.
+invoice_type: I direct, Q from a quotation, D from a delivery challan. A fourth value L exists on 13 old rows and is set by no live screen.
+tbl_invoice_credit_details has no reversal - a payment entered twice reduces inv_bal_value twice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="140.5769230769231" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Sales Receipt</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>lst_sales_receipt.php (list) &gt; pay_receipt.php (record, 693 lines) &gt; inc/datatable/ajaxReceiptlist.php &gt; inc/cis_ajax/jquery_modal_recipt_dets.php, inc/cis_ajax/modal_so_cash_details.php (view)</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Money in - AGAINST A SALES ORDER, NOT AN INVOICE</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Money received from a customer, recorded against THE SALES ORDER. Captures amount, date, mode (cash / cheque / card / transfer) with reference details, and WHICH LEDGER the money went into - the one place a customer's mst_ledger row is actually used. Advance payments work naturally: a receipt can precede any invoice.</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>tbl_receipt (W)
+tbl_receipt_details (W)
+tbl_sales_order (R for the list; W to record the receipt)
+mst_ledger (R - the ledger dropdown, ledger_status = 1)
+mst_supplier_new (R)
+mst_finyear (R)</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>INSERT tbl_receipt (so_id, supp_id, pay_slno, pay_finyr, ledger_id, pay_date, pay_type, pay_amount, pay_cardno, pay_refno, pay_chq_no, pay_chq_dt, pay_remarks, chq_passed).
+INSERT tbl_receipt_details - the breakdown rows.
+UPDATE tbl_sales_order - recording that a receipt exists.
+NO tbl_accounts ENTRY.</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>1. Accounts &gt; Sales Receipt - sales orders with what has been received against them.
+2. Choose an order; pay_receipt.php opens.
+3. Enter the date, the amount and the payment mode; cheque / card / transfer details appear as needed.
+4. Choose the LEDGER the money is going into.
+5. Save - receipt header and detail rows written, sales order updated.
+6. View receipts through the modals, or on the sales order print.</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Sales Order - the order shows what has been received; print_sales_order.php cash details; the receipt modals. NOT the Credit List, which reads tbl_invoice.inv_bal_value instead.</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>RECEIPTS AND INVOICE BALANCES ARE TWO SEPARATE SYSTEMS THAT NEVER MEET. A receipt is recorded against the SALES ORDER and updates nothing on the invoice; an invoice's inv_bal_value comes down only through mng_credit.php. So money taken here does NOT clear an invoice from the Credit List, and a credit payment there does not appear on the order. USING BOTH SCREENS DOUBLE-COUNTS - pick one route per customer.
+NOTHING CHECKS THE AMOUNT AGAINST WHAT IS OWED, and there is no reversal.
+chq_passed is never set by anything.
+The ledger dropdown lists EVERY active mst_ledger row, including auto-created customer, supplier and employee ledgers - and since nothing reads tbl_receipt.ledger_id afterwards, a wrong choice is never noticed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="85.76923076923076" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>GRN Payment Details</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>grn_payment_details.php (list) &gt; grn_pay_receipt.php (record, 892 lines) &gt; inc/datatable/ajaxGrnPaymentList.php &gt; grn_payment_details_pending.php</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Money out - the supplier side, AGAINST A GRN</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>The mirror of Sales Receipt on the buying side. Money paid to a supplier, recorded against a GRN - the goods receipt, not the purchase order and not the supplier's bill. The supplier's credit days set when payment is due. This and inv_bal_value are the WHOLE of BIE's money tracking.</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>tbl_grn_pay_receipt (W - one row per payment)
+tbl_grn (R for the list; W to record the payment)
+mst_supplier_new (R - the supplier and their credit days)
+mst_finyear (R)</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>INSERT tbl_grn_pay_receipt - the GRN, amount, date, mode, cheque and reference details.
+UPDATE tbl_grn - recording that a payment exists against it.
+NO tbl_accounts ENTRY.</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>1. Accounts &gt; GRN Payment Details - every GRN with its value, what has been paid and what is outstanding. grn_payment_details_pending.php narrows it to the unpaid ones.
+2. Choose a GRN; grn_pay_receipt.php opens.
+3. Enter the date, the amount and the payment mode with the cheque number or reference.
+4. Save - the payment row is written and the GRN updated.
+5. The list recalculates what is outstanding by summing payments against the GRN value.</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>GRN List - the GRN shows what has been paid; this list and its pending version. NOT the supplier's ledger, which nothing updates.</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>A PURCHASE RETURN DOES NOT REDUCE WHAT YOU OWE - purchase_return_add.php writes no accounting entry of any kind, so returned goods still show fully payable here. Check a GRN's returns before paying against it.
+PAYMENT IS TRACKED PER GRN, NOT PER SUPPLIER AND NOT PER BILL. No screen totals what is owed to one supplier, and the supplier's bill (supp_invoice_add.php) is a separate record this screen does not reconcile against.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:J8"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menu 10  ·  Report  (mm_id = 22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>14 reports and EVERY ONE IS READ-ONLY - not one writes a row. Six on stock, five on sales, one each on purchase cost, discounts and quotations. All of them print with the heading 'Day Book', which is a hardcoded string and means nothing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Sub-menu (form)</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>PHP file(s)</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>What it does (short)</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Tables used</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>What changes in the tables</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Full flow</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Where it reflects</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Key notes / traps</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="64" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Store Stock List</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>store_stock_list.php + inc/datatable/ajaxStoreStockList.php + inc/cis_ajax/jquery_modal_stock_det.php</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Read only</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Stock at YOUR branch as a searchable list, with BIN LOCATIONS. Reads branch_stock_field, branch_stock_location_rack_field and branch_stock_location_row_field from your mst_branch row. The heading carries your user name.</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>tbl_item_details (R)
+tbl_item_stock (R)
+mst_branch (R - three column names)</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>NOTHING - read only.</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>1. Report &gt; Store Stock List.
+2. Search and filter; the eye icon opens the item's stock detail in a modal.</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Nothing - it is a view. The one most people use for day-to-day stock enquiry.</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>Shows quantity, rack and row plus item code, description, category and UOM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="64" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Stock List (item-wise)</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>rpt_store_stock_list.php</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Read only</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>The same stock, laid out as a printable report rather than a searchable list. Filters on item and item type.</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>tbl_item_details (R)
+tbl_item_stock (R)
+mst_branch (R)</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>NOTHING - read only.</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>1. Report &gt; Stock List.
+2. Optionally filter by item and item type, then Report, then print.</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Nothing - it is a view.</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>Every report in this menu prints with the heading 'Day Book' - a hardcoded string in the print helper. There is no day book in BIE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="64" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Stock List (all branches)</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>rpt_all_store_stock_list.php</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Read only</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>THE ONLY SCREEN THAT SHOWS ALL THREE BRANCHES AT ONCE. Queries mst_branch for active branches and builds a column per branch, so HO, Kerala and Rajapalayam sit side by side for each item.</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>tbl_item_details (R)
+tbl_item_stock (R)
+mst_branch (R - the branch list)</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>NOTHING - read only.</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>1. Report &gt; Stock List (all branches).
+2. Optionally filter by item or item type, then Report.
+3. One row per item, one quantity column per branch.</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>Nothing - it is a view. USE THIS ONE when a branch says it has none and you want to know where the stock actually is.</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>A cosmetic bug in the heading: the item-type filter overwrites the item filter's heading text, and looks up item_type by passing an item_type_id as an item_id. The figures themselves are unaffected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="64" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Branch Wise Stock</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>rpt_branch_wise_stock.php</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Read only</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Stock for ONE CHOSEN branch - you pick the branch rather than being given your own. Filters on branch, item and item type.</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>tbl_item_details (R)
+tbl_item_stock (R)
+mst_branch (R)</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>NOTHING - read only.</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>1. Report &gt; Branch Wise Stock.
+2. Choose the branch, optionally an item or item type, then Report.</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Nothing - it is a view. Checking another branch's position.</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10" ht="109.2307692307692" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Item Stock History</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>rpt-item-stock-history.php</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Read only - THE AUDIT TRAIL</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Every movement of ONE item, in order, from tbl_stock_flow: transaction type, quantity moved, and the before and after figures. Only two types are recognised - GRN (goods in) and INV (invoiced out).</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>tbl_stock_flow (R)
+tbl_item_details (R)</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>NOTHING - read only.</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>1. Report &gt; Item Stock History.
+2. Choose the item, then Report.
+3. Columns: date, trans_type, before_qty, trans_qty, after_qty, price.</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Nothing - it is a view. Explaining how a stock figure got where it is.</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>ONLY TWO MOVEMENT TYPES ARE EVER WRITTEN AND ONLY TWO ARE RECOGNISED. tbl_stock_flow gets rows from the GRN and the three invoice screens. NOTHING ELSE writes a flow row - not the purchase return, not the delivery challan, not the price-update screen which also writes the stock column. So A MOVEMENT CAN CHANGE THE STOCK WITHOUT APPEARING HERE, and the running balance will not reconcile.
+THE BEFORE AND AFTER FIGURES ON A GRN ROW COME FROM THE BROWSER (see 8.2) while the real update re-reads the database. Treat trans_qty as reliable and before/after as indicative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="64" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>10.6</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Item Stock History Branch Wise</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>rpt_item_stock_history_branch_wise.php</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Read only</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>The same movements split by branch - tbl_stock_flow carries branch_id on every row, so the history can be read one branch at a time.</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>tbl_stock_flow (R)
+tbl_item_details (R)
+mst_branch (R)</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>NOTHING - read only.</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>1. Report &gt; Item Stock History Branch Wise.
+2. Choose the item and the branch, then Report.</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Nothing - it is a view.</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>All of 10.5's caveats apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="64" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>10.7</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Cost Worksheet</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>rpt_cost_worksheet.php + inc/datatable/ajaxCostWorkSheet.php</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Read only</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>What items cost to buy. Reads tbl_item_details and pulls the cost price out of YOUR branch's branch_item_cost_price column on tbl_item_stock.</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>tbl_item_details (R)
+tbl_item_stock (R)
+mst_branch (R - to resolve the column name)</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>NOTHING - read only.</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>1. Report &gt; Cost Worksheet.
+2. The list loads through ajaxCostWorkSheet.php, resolving your branch's cost column.
+3. Search, filter, print.</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>Nothing - it is a view.</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>THE COST SHOWN IS THE ITEM'S CURRENT COST PRICE, NOT A PURCHASE HISTORY. It changes the moment someone runs an Item Price Update, and it changes for your branch only - two branches show two different worksheets for the same item. For what a specific purchase actually cost, use the purchase order and the GRN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="64" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>10.8</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Credit List</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>rpt_credit_list.php</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Read only - BIE'S RECEIVABLES</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Invoices with money still outstanding. For each invoice it sums tbl_invoice_credit_details.paid_amount and shows it against the invoice value: invoiced, paid, outstanding. Filters on customer.</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>tbl_invoice (R)
+tbl_invoice_details (R)
+tbl_invoice_credit_details (R - SUM(paid_amount))
+mst_supplier_new (R)</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>NOTHING - read only.</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>1. Report &gt; Credit List.
+2. Optionally choose a customer, then Report.
+3. Invoice reference and date, customer, value, paid, outstanding.</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Nothing - it is a view. This and GRN Payment Details are the whole of BIE's money tracking (see 9.1).</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>THIS REPORT DOES NOT KNOW ABOUT SALES RECEIPTS. It reads only the credit payments entered through mng_credit.php against the invoice. Money taken through Sales Receipt (9.2) is recorded against the SALES ORDER and leaves the invoice showing unpaid here. If customers appear to owe money they have already paid, this is why.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="64" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>10.9</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Quotation Branch Report</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>quotation_branch_rept.php</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Read only</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Quotations raised, per branch, with their value and state. Filters on branch.</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>tbl_quotation (R)
+mst_supplier_new (R)
+mst_branch (R)</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>NOTHING - read only.</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>1. Report &gt; Quotation Branch Report.
+2. Choose the branch, then Report.
+3. Quotation reference, version, date, customer, value, verify and approve state.</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>Nothing - it is a view. Sales-pipeline review; seeing what is stuck waiting for approval.</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>BECAUSE QUOTATIONS ARE VERSIONED (6.1), a quotation revised three times appears as THREE ROWS. Read quo_version before totalling anything or you will count the same opportunity several times.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="64" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>10.10</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Sales List</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>rpt_sales_list.php</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Read only</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>What was sold, line by line, out of tbl_invoice_details. Filters on customer.</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>tbl_invoice (R)
+tbl_invoice_details (R)
+tbl_item_details (R)
+mst_supplier_new (R)</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>NOTHING - read only.</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>1. Report &gt; Sales List.
+2. Optionally choose a customer, then Report.
+3. Invoice, date, customer, item, quantity, rate, value.</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Nothing - it is a view. Sales analysis by item or customer.</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16" ht="64" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>10.11</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Invoice Report</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>invoice_report.php</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Read only</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Invoices at header level with their values. For each it sums the line net values and the packing charges, and separately sums the packing rows whose inv_pack_decp is 2, 5, 11 or 15 - the insurance-type charges. Filters on BRANCH and CUSTOMER.</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>tbl_invoice (R)
+tbl_invoice_details (R - SUM(net_value))
+tbl_invoice_pack_details (R - SUM(inv_pack_total))
+mst_supplier_new (R)
+mst_branch (R)</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>NOTHING - read only.</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>1. Report &gt; Invoice Report.
+2. Choose branch and / or customer, then Report.
+3. Invoice reference, date, customer, net value, packing, insurance, total.</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>Nothing - it is a view. Monthly sales totals; reconciling invoice values.</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>The insurance figure is identified by hardcoded inv_pack_decp values (2, 5, 11, 15). If the packing-charge types are ever renumbered, this column silently becomes wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="75" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>10.12</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Sales Order Report</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>rpt_sales_order.php (823 lines - the largest report)</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Read only</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Orders raised and where each one has got to. Filters on branch.</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>tbl_sales_order (R)
+tbl_sales_order_details (R)
+tbl_quotation (R)
+tbl_dc (R)
+tbl_invoice (R)
+mst_supplier_new (R)</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>NOTHING - read only.</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>1. Report &gt; Sales Order Report.
+2. Choose the branch, then Report.
+3. Order reference and date, customer, despatch date, value, whether a challan and an invoice exist.</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Nothing - it is a view. Order book and delivery chasing.</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18" ht="74.03846153846153" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>10.13</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>SO Stock List Branchwise</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>rpt_so_stock_list_branchwise.php</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Read only</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>ORDERED BUT NOT YET DESPATCHED, SET AGAINST STOCK. For each item it sums so_qty over orders where dc_status = 0 and so_cancel_status = 0 for the chosen branch and financial year, and shows it beside the stock held. The one report that answers 'can we actually deliver what we have promised?'</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>tbl_sales_order (R)
+tbl_sales_order_details (R)
+tbl_item_details (R)
+tbl_item_stock (R)
+mst_branch (R)</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>NOTHING - read only.</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>1. Report &gt; SO Stock List Branchwise.
+2. Choose the branch and the financial year, then Report.
+3. Item, pending order quantity, stock at that branch.</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>Nothing - it is a view. Deciding what to buy or make next - the closest BIE gets to a shortage report.</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>PENDING IS DEFINED AS 'NO DELIVERY CHALLAN YET' (dc_status = 0). Because dc_status is a flag rather than a count (6.2), an order that has been PARTLY despatched counts as fully despatched and drops out. The pending figure is a LOWER BOUND.
+There is dead code that appends SQL text to the quantity variable when a financial year is chosen; the subsequent (float) cast makes it harmless.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="135" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>10.14</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Item Discount</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>rpt_item_discount.php</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Read only - ALL BRANCHES AT ONCE</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>The minimum and maximum discount allowed for every item, for EVERY BRANCH SIDE BY SIDE. The discount equivalent of the all-branches stock report - the one place you can see whether the three branches sell on the same terms. Filters on item.</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>tbl_item_details (R)
+tbl_item_stock (R)
+mst_branch (R - the branch list)</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>NOTHING - read only.</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>1. Report &gt; Item Discount, optionally choose an item.
+2. The page reads the active branches, builds a pair of columns for each, and runs one query joining tbl_item_details to tbl_item_stock.
+3. Every item is listed with its min and max discount per branch.</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Nothing - it is a view.</t>
+        </is>
+      </c>
+      <c r="J19" s="10" t="inlineStr">
+        <is>
+          <t>THIS REPORT GUESSES THE COLUMN NAMES INSTEAD OF LOOKING THEM UP. It builds them as strtolower(branch_code) . '_item_min_discount' rather than reading branch_item_min_discount from the branch row as every other screen does. True of the three branches as shipped, and not guaranteed - add a branch whose stored column names do not match its code and this report shows blank columns for it while everything else works. IF YOU FIX ONE THING IN THIS MENU, FIX THIS.
+The discount columns come from tbl_item_stock, so they are whatever the last Item Price Update for that branch set. An item never price-updated at a branch shows the figures the item form wrote at creation, which were the same for all three.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:J19"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menu 11  ·  Service  (mm_id = 25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2 screens for after-sales work: which spare parts fit which product, and repairs booked in against an invoice the customer already has. The repair consumes parts and moves no stock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Sub-menu (form)</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>PHP file(s)</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>What it does (short)</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Tables used</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>What changes in the tables</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Full flow</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Where it reflects</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Key notes / traps</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="82.69230769230769" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Spare Mapping</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>spare_mapping_list.php (list) &gt; spare_mapping.php (map, 331 lines) &gt; inc/datatable/ajaxMappingList.php</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Master - a link table between items</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Which spare parts belong to which product. One product, many spares - and both sides are ordinary rows in tbl_item_details, so a spare is just another item mapped to a parent. It exists so that a repair coming in for a product can be offered the right parts.</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>tbl_spare_mapping (RW)
+tbl_item_details (R - BOTH sides, the product and the spares)</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>DELETE FROM tbl_spare_mapping WHERE item_id = &lt;this product&gt; - EVERY row, before writing.
+INSERT tbl_spare_mapping - one row per chosen spare (item_id, spare_item_id, created_by, created_dtm).</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>1. Service &gt; Spare Mapping - products that have spares mapped, with how many each has.
+2. Choose a product, or add a new mapping; spare_mapping.php opens.
+3. Pick the spares that belong to it - all at once; this is a set, not a sequence.
+4. Save - every existing mapping for the product is deleted first, then the chosen spares inserted.
+5. The dustbin on the list removes a mapping through the shared delete endpoint.</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Repair Indent - the parts offered for a product being repaired. Nothing else.</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>SAVING REBUILDS THE WHOLE MAPPING - open a product with forty spares, tick one more, and save a form that did not post the other forty, and you are left with one. Check the count after saving.
+THERE IS NO STATUS COLUMN - tbl_spare_mapping has only the two ids and the audit pair, so unlike everywhere else in BIE, removing a mapping really removes it.
+Nothing stops a circular mapping or an item being mapped as a spare of itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="152.8846153846154" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Repair Indent</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>repair_indent_list.php (list) &gt; repair_indent_add.php (book, 961 lines) &gt; inc/datatable/ajaxIndentList.php &gt; sales_repair_print.php &gt; inc/cis_ajax/jquery_sales_repair_status.php (verify and approve)</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Transaction with two-step approval - AND IT MOVES NO STOCK</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>A repair booked in for something the customer already bought. Raised AGAINST THE INVOICE (inv_id), so the repair is tied to the actual sale and through it to the sales order and the quotation. Lines are the parts and labour, priced with tax. Then the same verify-then-approve pattern as a quotation.</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>tbl_sales_repair (RW)
+tbl_sales_repair_details (RW)
+tbl_invoice (R - the invoice being repaired against; the stamp update is COMMENTED OUT)
+tbl_spare_mapping (R - the parts that fit)
+tbl_item_details (R)
+mst_supplier_new (R)
+mst_finyear (R)
+tbl_accounts - NOTHING (the posting code exists, commented out)</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>INSERT tbl_sales_repair (sal_repair_finyr, sal_repair_slno, sal_repair_date, so_id, inv_id, supp_id, company_id, modify_by, modify_date_time).
+DELETE + INSERT tbl_sales_repair_details - the lines, rebuilt on every save.
+VERIFY (jquery_sales_repair_status.php, mode = verify): UPDATE sal_repair_verify_status, _verify_by, _verify_date_time.
+APPROVE (mode = approve): UPDATE sal_repair_approve_status, _approve_by, _approve_date_time.
+NO tbl_item_stock UPDATE. NO tbl_stock_flow ROW. NO tbl_accounts ENTRY. NO tbl_invoice STAMP.</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>1. Service &gt; Repair Indent - repairs booked, with value and approval state.
+2. Add New; the serial is MAX(sal_repair_slno) + 1 for your branch, and the financial year comes from mst_finyear.
+3. Choose the INVOICE being repaired against - that brings the customer, the sales order and the quotation with it.
+4. Add the lines - spare parts and labour - with quantities, rates and tax.
+5. Save - header, then lines.
+6. VERIFY, then APPROVE, through jquery_sales_repair_status.php.
+7. Print with sales_repair_print.php. The quotation action on the list opens quotation.php, so a repair can be quoted for.</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Repair Indent List; sales_repair_print.php (the job sheet); Quotation - a repair can be quoted for. NOT the stock reports. NOT the invoice, which is not stamped.</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>PARTS USED IN A REPAIR NEVER LEAVE STOCK - no stock table is touched and no tbl_stock_flow row written. With purchase returns (8.3) this is the second standing reason stock reads high.
+THREE THINGS ARE WRITTEN AND THEN COMMENTED OUT: the tbl_accounts posting in jquery_sales_repair_status.php, the tbl_invoice.repair_submit_status stamp, and with it any way of telling from the invoice that a repair exists. The code reads as though the feature was built and switched off - it even looks up a sales ledger from mst_accounts_setting, a table BIE does not otherwise use.
+A REPAIR CAN BE BOOKED AGAINST AN INVOICE MORE THAN ONCE with no warning, because the invoice is never stamped.
+company_id on tbl_sales_repair really holds a BRANCH id - the serial is computed WHERE company_id = &lt;your branch&gt;.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:J7"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1501,14 +2998,14 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tables Reference - Phases 1 and 2</t>
+          <t>Tables Reference - complete</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every table touched so far. The system has 105 tables in total; the rest arrive with Accounts, Report and Service.</t>
+          <t>Every table the live menu touches, across all 11 menus. The database holds 105 in total; the remainder belong to legacy screens the menu does not open.</t>
         </is>
       </c>
     </row>
@@ -3538,14 +5035,419 @@
         </is>
       </c>
     </row>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t>tbl_invoice</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>transaction</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>THE STEP THAT REDUCES STOCK. invoice_type I direct / Q from quotation / D from challan. inv_bal_value is BIE's only receivables figure.</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>9.1, 10.8, 10.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="16" customHeight="1">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>tbl_invoice_details</t>
+        </is>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>Invoice lines. Rebuilt on every save.</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>9.1, 10.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="16" customHeight="1">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t>tbl_invoice_pack_details</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>Packing charges. inv_pack_decp 2/5/11/15 are the insurance types.</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>9.1, 10.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="16" customHeight="1">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>tbl_invoice_denomination_details</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>The note breakdown for a cash invoice.</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t>tbl_invoice_credit_details</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>transaction</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>One row per part-payment against a credit invoice. The ONLY thing that reduces inv_bal_value.</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>9.1, 10.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>tbl_receipt</t>
+        </is>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>transaction</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>Money in, against a SALES ORDER (so_id), not an invoice. Carries ledger_id - the only real use of a customer's ledger.</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="11" t="inlineStr">
+        <is>
+          <t>tbl_receipt_details</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>Receipt breakdown rows.</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="30" customHeight="1">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t>tbl_grn_pay_receipt</t>
+        </is>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>transaction</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>Money out, against a GRN. Summed against the GRN value to get what is outstanding.</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="11" t="inlineStr">
+        <is>
+          <t>tbl_accounts</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>journal</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>WRITE-ONLY. Four files insert (all payroll); a fifth's insert is commented out; NOTHING reads it. There is no Day Book, Ledger Book or Trial Balance in BIE.</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>3.5, 3.6, 5.2-5.4 (writes only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>mst_ledger</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>Ledgers, auto-created for every customer, supplier and employee - then barely used. Read as a dropdown on the receipt screen and as the dr/cr side of the payroll journal nothing reads.</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>2.1, 2.2, 3.1, 9.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="11" t="inlineStr">
+        <is>
+          <t>mst_accounts_group</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>Ledger groups; supplies ledger_type when a ledger is auto-created.</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>2.1, 2.2, 3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" s="12" t="inlineStr">
+        <is>
+          <t>mst_accounts_setting</t>
+        </is>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>setup</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>Referenced only by commented-out code in the repair status endpoint. Unused.</t>
+        </is>
+      </c>
+      <c r="E91" s="10" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="11" t="inlineStr">
+        <is>
+          <t>tbl_spare_mapping</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t>Which spares fit which product. NO status column - deletes here are real.</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t>tbl_sales_repair</t>
+        </is>
+      </c>
+      <c r="B93" s="10" t="inlineStr">
+        <is>
+          <t>transaction</t>
+        </is>
+      </c>
+      <c r="C93" s="10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>Repairs, raised against an invoice. Two-step verify / approve. company_id actually holds a BRANCH id.</t>
+        </is>
+      </c>
+      <c r="E93" s="10" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="11" t="inlineStr">
+        <is>
+          <t>tbl_sales_repair_details</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>Parts and labour lines, with tax. Rebuilt on every save.</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:E79"/>
+  <autoFilter ref="A5:E94"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3574,7 +5476,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Menu order follows the sidebar. Update the Status column as each phase lands - the totals below recalculate.</t>
+          <t>All 11 menus and all 63 live screens are documented. Menu order follows the sidebar; the totals below are live formulas.</t>
         </is>
       </c>
     </row>
@@ -3926,12 +5828,16 @@
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="G14" s="15" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr"/>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>No general ledger - money is tracked per document</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="n">
@@ -3958,14 +5864,14 @@
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>Largest menu - 14 reports</t>
+          <t>Largest menu - 14 reports, all read-only</t>
         </is>
       </c>
     </row>
@@ -3994,75 +5900,79 @@
           <t>Phase 3</t>
         </is>
       </c>
-      <c r="G16" s="15" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="inlineStr"/>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>The repair consumes parts and moves no stock</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Menus in the system</t>
         </is>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="16">
         <f>COUNTA(B6:B16)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Menus documented</t>
         </is>
       </c>
-      <c r="C19" s="18">
+      <c r="C19" s="16">
         <f>COUNTIF(G6:G16,"Done")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Screens in the system</t>
         </is>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="16">
         <f>SUM(D6:D16)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Screens documented</t>
         </is>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="16">
         <f>SUMIF(G6:G16,"Done",D6:D16)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Screens remaining</t>
         </is>
       </c>
-      <c r="C22" s="18">
+      <c r="C22" s="16">
         <f>SUMIF(G6:G16,"Pending",D6:D16)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Percent complete</t>
         </is>
       </c>
-      <c r="C23" s="19">
+      <c r="C23" s="17">
         <f>IFERROR(SUMIF(G6:G16,"Done",D6:D16)/SUM(D6:D16),0)</f>
         <v/>
       </c>
@@ -4583,7 +6493,7 @@
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>Phase 2 / 3</t>
+          <t>Part 4</t>
         </is>
       </c>
     </row>
@@ -4773,7 +6683,7 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>Phase 2 / 3</t>
+          <t>Part 5</t>
         </is>
       </c>
     </row>
@@ -4873,7 +6783,7 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>Phase 2 / 3</t>
+          <t>Part 6</t>
         </is>
       </c>
     </row>
@@ -4919,7 +6829,7 @@
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>Phase 2 / 3</t>
+          <t>Part 7</t>
         </is>
       </c>
     </row>
@@ -4965,7 +6875,7 @@
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>Phase 2 / 3</t>
+          <t>Part 8</t>
         </is>
       </c>
     </row>
@@ -5047,7 +6957,7 @@
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>Phase 2 / 3</t>
+          <t>Part 9</t>
         </is>
       </c>
     </row>
@@ -5111,7 +7021,7 @@
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>Phase 2 / 3</t>
+          <t>Part 10</t>
         </is>
       </c>
     </row>
@@ -5373,7 +7283,7 @@
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>Phase 2 / 3</t>
+          <t>Part 11</t>
         </is>
       </c>
     </row>
